--- a/ROSA_vitaSPEC/Data/Analyses_chimiques_new_FRUIT.xlsx
+++ b/ROSA_vitaSPEC/Data/Analyses_chimiques_new_FRUIT.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q307"/>
+  <dimension ref="A1:U307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,32 +412,52 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>trans-alpha-carotène</t>
+          <t>trans.alpha.carotene</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>trans-beta-carotène</t>
+          <t>trans.beta.carotene</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>13.cis-beta-carotène</t>
+          <t>total.trans.carotene.natif</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>9.cis-beta-carotène</t>
+          <t>ratio.alpha.beta</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>total.beta-carotènes</t>
+          <t>ratio.alpha.natif</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>total.carotènes</t>
+          <t>ratio.beta.natif</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>X13.cis.beta.carotene</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>X9.cis.beta.carotene</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>total.beta.carotene</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
         </is>
       </c>
     </row>
@@ -491,15 +511,27 @@
         <v>308.0702634771758</v>
       </c>
       <c r="N3">
+        <v>494.0537302522589</v>
+      </c>
+      <c r="O3">
+        <v>0.603704702543815</v>
+      </c>
+      <c r="P3">
+        <v>0.3764438063854347</v>
+      </c>
+      <c r="Q3">
+        <v>0.6235561936145654</v>
+      </c>
+      <c r="R3">
         <v>70.9672988204909</v>
       </c>
-      <c r="O3">
+      <c r="S3">
         <v>58.91171408675048</v>
       </c>
-      <c r="P3">
+      <c r="T3">
         <v>437.9492763844171</v>
       </c>
-      <c r="Q3">
+      <c r="U3">
         <v>623.9327431595003</v>
       </c>
     </row>
@@ -537,7 +569,7 @@
         <v>0.4</v>
       </c>
       <c r="K4">
-        <v>82.2</v>
+        <v>82.21396605551794</v>
       </c>
       <c r="L4">
         <v>224.9995994937852</v>
@@ -546,15 +578,27 @@
         <v>361.0346103457543</v>
       </c>
       <c r="N4">
+        <v>586.0342098395396</v>
+      </c>
+      <c r="O4">
+        <v>0.6232078394874896</v>
+      </c>
+      <c r="P4">
+        <v>0.3839359472809475</v>
+      </c>
+      <c r="Q4">
+        <v>0.6160640527190524</v>
+      </c>
+      <c r="R4">
         <v>71.62144319195173</v>
       </c>
-      <c r="O4">
+      <c r="S4">
         <v>66.78624027603922</v>
       </c>
-      <c r="P4">
+      <c r="T4">
         <v>499.4422938137453</v>
       </c>
-      <c r="Q4">
+      <c r="U4">
         <v>724.4418933075306</v>
       </c>
     </row>
@@ -612,7 +656,7 @@
         <v>0.4</v>
       </c>
       <c r="K7">
-        <v>83.8</v>
+        <v>83.81459579780338</v>
       </c>
       <c r="L7">
         <v>984.0783457590778</v>
@@ -621,15 +665,27 @@
         <v>890.0218702780273</v>
       </c>
       <c r="N7">
+        <v>1874.100216037105</v>
+      </c>
+      <c r="O7">
+        <v>1.105678836242158</v>
+      </c>
+      <c r="P7">
+        <v>0.5250937689127262</v>
+      </c>
+      <c r="Q7">
+        <v>0.4749062310872739</v>
+      </c>
+      <c r="R7">
         <v>65.11484824835189</v>
       </c>
-      <c r="O7">
+      <c r="S7">
         <v>123.6424813282191</v>
       </c>
-      <c r="P7">
+      <c r="T7">
         <v>1078.779199854598</v>
       </c>
-      <c r="Q7">
+      <c r="U7">
         <v>2062.857545613676</v>
       </c>
     </row>
@@ -667,7 +723,7 @@
         <v>0.4</v>
       </c>
       <c r="K8">
-        <v>76.59999999999999</v>
+        <v>76.56487923738754</v>
       </c>
       <c r="L8">
         <v>186.7703284880623</v>
@@ -676,15 +732,27 @@
         <v>148.9159858200287</v>
       </c>
       <c r="N8">
+        <v>335.686314308091</v>
+      </c>
+      <c r="O8">
+        <v>1.25419932225263</v>
+      </c>
+      <c r="P8">
+        <v>0.5563835060509662</v>
+      </c>
+      <c r="Q8">
+        <v>0.4436164939490337</v>
+      </c>
+      <c r="R8">
         <v>20.27847819205311</v>
       </c>
-      <c r="O8">
+      <c r="S8">
         <v>29.43650060136741</v>
       </c>
-      <c r="P8">
+      <c r="T8">
         <v>198.6309646134492</v>
       </c>
-      <c r="Q8">
+      <c r="U8">
         <v>385.4012931015116</v>
       </c>
     </row>
@@ -762,7 +830,7 @@
         <v>0.4</v>
       </c>
       <c r="K13">
-        <v>80.90000000000001</v>
+        <v>80.93983810661194</v>
       </c>
       <c r="L13">
         <v>466.9272710927087</v>
@@ -771,15 +839,27 @@
         <v>672.245252102852</v>
       </c>
       <c r="N13">
+        <v>1139.172523195561</v>
+      </c>
+      <c r="O13">
+        <v>0.694578756238311</v>
+      </c>
+      <c r="P13">
+        <v>0.4098828417866885</v>
+      </c>
+      <c r="Q13">
+        <v>0.5901171582133116</v>
+      </c>
+      <c r="R13">
         <v>93.07929097309515</v>
       </c>
-      <c r="O13">
+      <c r="S13">
         <v>140.7611407738249</v>
       </c>
-      <c r="P13">
+      <c r="T13">
         <v>906.0856838497721</v>
       </c>
-      <c r="Q13">
+      <c r="U13">
         <v>1373.012954942481</v>
       </c>
     </row>
@@ -837,7 +917,7 @@
         <v>0.6</v>
       </c>
       <c r="K16">
-        <v>80.5</v>
+        <v>80.47010596150503</v>
       </c>
     </row>
     <row r="17">
@@ -894,7 +974,7 @@
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>76.3</v>
+        <v>76.28058633358451</v>
       </c>
       <c r="L19">
         <v>577.6362207862151</v>
@@ -903,15 +983,27 @@
         <v>719.0866146083104</v>
       </c>
       <c r="N19">
+        <v>1296.722835394525</v>
+      </c>
+      <c r="O19">
+        <v>0.8032915771917908</v>
+      </c>
+      <c r="P19">
+        <v>0.4454585089576759</v>
+      </c>
+      <c r="Q19">
+        <v>0.5545414910423241</v>
+      </c>
+      <c r="R19">
         <v>72.29196866482411</v>
       </c>
-      <c r="O19">
+      <c r="S19">
         <v>251.526634878552</v>
       </c>
-      <c r="P19">
+      <c r="T19">
         <v>1042.905218151687</v>
       </c>
-      <c r="Q19">
+      <c r="U19">
         <v>1620.541438937901</v>
       </c>
     </row>
@@ -969,7 +1061,7 @@
         <v>0.5</v>
       </c>
       <c r="K22">
-        <v>82</v>
+        <v>81.95152487913626</v>
       </c>
       <c r="L22">
         <v>178.4500742455266</v>
@@ -978,15 +1070,27 @@
         <v>449.4155718610121</v>
       </c>
       <c r="N22">
+        <v>627.8656461065386</v>
+      </c>
+      <c r="O22">
+        <v>0.3970714087777865</v>
+      </c>
+      <c r="P22">
+        <v>0.2842169743672303</v>
+      </c>
+      <c r="Q22">
+        <v>0.7157830256327697</v>
+      </c>
+      <c r="R22">
         <v>45.75663213510247</v>
       </c>
-      <c r="O22">
+      <c r="S22">
         <v>73.3961134041708</v>
       </c>
-      <c r="P22">
+      <c r="T22">
         <v>568.5683174002853</v>
       </c>
-      <c r="Q22">
+      <c r="U22">
         <v>747.0183916458119</v>
       </c>
     </row>
@@ -1054,7 +1158,7 @@
         <v>0.6</v>
       </c>
       <c r="K26">
-        <v>79.59999999999999</v>
+        <v>79.63429565134498</v>
       </c>
       <c r="L26">
         <v>223.4824598004603</v>
@@ -1063,15 +1167,27 @@
         <v>404.2018467396107</v>
       </c>
       <c r="N26">
+        <v>627.684306540071</v>
+      </c>
+      <c r="O26">
+        <v>0.5528981661096395</v>
+      </c>
+      <c r="P26">
+        <v>0.3560427709788428</v>
+      </c>
+      <c r="Q26">
+        <v>0.643957229021157</v>
+      </c>
+      <c r="R26">
         <v>54.47443435078496</v>
       </c>
-      <c r="O26">
+      <c r="S26">
         <v>54.17839374982388</v>
       </c>
-      <c r="P26">
+      <c r="T26">
         <v>512.8546748402196</v>
       </c>
-      <c r="Q26">
+      <c r="U26">
         <v>736.3371346406798</v>
       </c>
     </row>
@@ -1109,7 +1225,7 @@
         <v>0.5</v>
       </c>
       <c r="K27">
-        <v>79.2</v>
+        <v>79.23304692735496</v>
       </c>
       <c r="L27">
         <v>144.8503322598701</v>
@@ -1118,15 +1234,27 @@
         <v>95.06852596962841</v>
       </c>
       <c r="N27">
+        <v>239.9188582294985</v>
+      </c>
+      <c r="O27">
+        <v>1.523641297500979</v>
+      </c>
+      <c r="P27">
+        <v>0.6037471723932224</v>
+      </c>
+      <c r="Q27">
+        <v>0.3962528276067777</v>
+      </c>
+      <c r="R27">
         <v>10.33634239077255</v>
       </c>
-      <c r="O27">
+      <c r="S27">
         <v>21.12239568514136</v>
       </c>
-      <c r="P27">
+      <c r="T27">
         <v>126.5272640455423</v>
       </c>
-      <c r="Q27">
+      <c r="U27">
         <v>271.3775963054125</v>
       </c>
     </row>
@@ -1174,7 +1302,7 @@
         <v>0.4</v>
       </c>
       <c r="K29">
-        <v>83.90000000000001</v>
+        <v>83.91986287985885</v>
       </c>
       <c r="L29">
         <v>278.3478037446595</v>
@@ -1183,15 +1311,27 @@
         <v>279.5624689344854</v>
       </c>
       <c r="N29">
+        <v>557.9102726791449</v>
+      </c>
+      <c r="O29">
+        <v>0.9956551206803425</v>
+      </c>
+      <c r="P29">
+        <v>0.4989114152854787</v>
+      </c>
+      <c r="Q29">
+        <v>0.5010885847145213</v>
+      </c>
+      <c r="R29">
         <v>32.81686560001047</v>
       </c>
-      <c r="O29">
+      <c r="S29">
         <v>57.36041064848659</v>
       </c>
-      <c r="P29">
+      <c r="T29">
         <v>369.7397451829825</v>
       </c>
-      <c r="Q29">
+      <c r="U29">
         <v>648.0875489276419</v>
       </c>
     </row>
@@ -1369,7 +1509,7 @@
         <v>0.5</v>
       </c>
       <c r="K44">
-        <v>84</v>
+        <v>84.04606481385339</v>
       </c>
       <c r="L44">
         <v>445.5204167255083</v>
@@ -1378,15 +1518,27 @@
         <v>1051.809098637242</v>
       </c>
       <c r="N44">
+        <v>1497.32951536275</v>
+      </c>
+      <c r="O44">
+        <v>0.4235753591623605</v>
+      </c>
+      <c r="P44">
+        <v>0.2975433344193275</v>
+      </c>
+      <c r="Q44">
+        <v>0.7024566655806725</v>
+      </c>
+      <c r="R44">
         <v>88.78066317461675</v>
       </c>
-      <c r="O44">
+      <c r="S44">
         <v>217.3517275194484</v>
       </c>
-      <c r="P44">
+      <c r="T44">
         <v>1357.941489331307</v>
       </c>
-      <c r="Q44">
+      <c r="U44">
         <v>1803.461906056815</v>
       </c>
     </row>
@@ -1424,7 +1576,7 @@
         <v>0.5</v>
       </c>
       <c r="K45">
-        <v>85.8</v>
+        <v>85.77469510516093</v>
       </c>
       <c r="L45">
         <v>61.35125606815558</v>
@@ -1433,15 +1585,27 @@
         <v>126.0444149104736</v>
       </c>
       <c r="N45">
+        <v>187.3956709786291</v>
+      </c>
+      <c r="O45">
+        <v>0.4867431540836772</v>
+      </c>
+      <c r="P45">
+        <v>0.3273888652163804</v>
+      </c>
+      <c r="Q45">
+        <v>0.6726111347836197</v>
+      </c>
+      <c r="R45">
         <v>34.08150109916822</v>
       </c>
-      <c r="O45">
+      <c r="S45">
         <v>35.28573746347126</v>
       </c>
-      <c r="P45">
+      <c r="T45">
         <v>195.4116534731131</v>
       </c>
-      <c r="Q45">
+      <c r="U45">
         <v>256.7629095412686</v>
       </c>
     </row>
@@ -1489,7 +1653,7 @@
         <v>0.4</v>
       </c>
       <c r="K47">
-        <v>80.3</v>
+        <v>80.27076085178939</v>
       </c>
       <c r="L47">
         <v>330.1216686372389</v>
@@ -1498,15 +1662,27 @@
         <v>302.9693738068675</v>
       </c>
       <c r="N47">
+        <v>633.0910424441065</v>
+      </c>
+      <c r="O47">
+        <v>1.089620592633499</v>
+      </c>
+      <c r="P47">
+        <v>0.521444226035443</v>
+      </c>
+      <c r="Q47">
+        <v>0.4785557739645568</v>
+      </c>
+      <c r="R47">
         <v>53.09586007853833</v>
       </c>
-      <c r="O47">
+      <c r="S47">
         <v>81.6042350866249</v>
       </c>
-      <c r="P47">
+      <c r="T47">
         <v>437.6694689720308</v>
       </c>
-      <c r="Q47">
+      <c r="U47">
         <v>767.7911376092698</v>
       </c>
     </row>
@@ -1560,15 +1736,27 @@
         <v>108.9125147812613</v>
       </c>
       <c r="N49">
+        <v>233.4974731546526</v>
+      </c>
+      <c r="O49">
+        <v>1.143899382211551</v>
+      </c>
+      <c r="P49">
+        <v>0.533560199561024</v>
+      </c>
+      <c r="Q49">
+        <v>0.466439800438976</v>
+      </c>
+      <c r="R49">
         <v>29.76476574124128</v>
       </c>
-      <c r="O49">
+      <c r="S49">
         <v>21.32894762759781</v>
       </c>
-      <c r="P49">
+      <c r="T49">
         <v>160.0062281501004</v>
       </c>
-      <c r="Q49">
+      <c r="U49">
         <v>284.5911865234917</v>
       </c>
     </row>
@@ -1606,7 +1794,7 @@
         <v>0.4</v>
       </c>
       <c r="K50">
-        <v>82.09999999999999</v>
+        <v>82.10035848610701</v>
       </c>
       <c r="L50">
         <v>25.05443569258104</v>
@@ -1615,15 +1803,27 @@
         <v>42.59448186716774</v>
       </c>
       <c r="N50">
+        <v>67.64891755974878</v>
+      </c>
+      <c r="O50">
+        <v>0.5882084860361515</v>
+      </c>
+      <c r="P50">
+        <v>0.3703597425701971</v>
+      </c>
+      <c r="Q50">
+        <v>0.629640257429803</v>
+      </c>
+      <c r="R50">
         <v>4.060843887896338</v>
       </c>
-      <c r="O50">
+      <c r="S50">
         <v>8.959460659806417</v>
       </c>
-      <c r="P50">
+      <c r="T50">
         <v>55.6147864148705</v>
       </c>
-      <c r="Q50">
+      <c r="U50">
         <v>80.66922210745153</v>
       </c>
     </row>
@@ -1671,7 +1871,7 @@
         <v>0.5</v>
       </c>
       <c r="K52">
-        <v>82</v>
+        <v>82.01470529606038</v>
       </c>
       <c r="L52">
         <v>1530.279969081423</v>
@@ -1680,15 +1880,27 @@
         <v>917.8779964620762</v>
       </c>
       <c r="N52">
+        <v>2448.157965543499</v>
+      </c>
+      <c r="O52">
+        <v>1.667193216287813</v>
+      </c>
+      <c r="P52">
+        <v>0.6250740314225172</v>
+      </c>
+      <c r="Q52">
+        <v>0.3749259685774828</v>
+      </c>
+      <c r="R52">
         <v>186.5123325003927</v>
       </c>
-      <c r="O52">
+      <c r="S52">
         <v>108.7828735958916</v>
       </c>
-      <c r="P52">
+      <c r="T52">
         <v>1213.17320255836</v>
       </c>
-      <c r="Q52">
+      <c r="U52">
         <v>2743.453171639783</v>
       </c>
     </row>
@@ -1726,7 +1938,7 @@
         <v>0.4</v>
       </c>
       <c r="K53">
-        <v>77.7</v>
+        <v>77.66225709964002</v>
       </c>
       <c r="L53">
         <v>99.38402988415841</v>
@@ -1735,15 +1947,27 @@
         <v>126.0045909451201</v>
       </c>
       <c r="N53">
+        <v>225.3886208292785</v>
+      </c>
+      <c r="O53">
+        <v>0.7887334035903822</v>
+      </c>
+      <c r="P53">
+        <v>0.4409451973151619</v>
+      </c>
+      <c r="Q53">
+        <v>0.5590548026848381</v>
+      </c>
+      <c r="R53">
         <v>12.08160769556757</v>
       </c>
-      <c r="O53">
+      <c r="S53">
         <v>41.1002817351888</v>
       </c>
-      <c r="P53">
+      <c r="T53">
         <v>179.1864803758764</v>
       </c>
-      <c r="Q53">
+      <c r="U53">
         <v>278.5705102600348</v>
       </c>
     </row>
@@ -1780,6 +2004,9 @@
       <c r="J54">
         <v>0.4253099208533411</v>
       </c>
+      <c r="K54">
+        <v>88.01054728477756</v>
+      </c>
       <c r="L54">
         <v>93.40845178286796</v>
       </c>
@@ -1787,15 +2014,27 @@
         <v>98.87536151223627</v>
       </c>
       <c r="N54">
+        <v>192.2838132951042</v>
+      </c>
+      <c r="O54">
+        <v>0.9447090797367982</v>
+      </c>
+      <c r="P54">
+        <v>0.4857842695240861</v>
+      </c>
+      <c r="Q54">
+        <v>0.514215730475914</v>
+      </c>
+      <c r="R54">
         <v>2.252583242132773</v>
       </c>
-      <c r="O54">
+      <c r="S54">
         <v>13.23612015685754</v>
       </c>
-      <c r="P54">
+      <c r="T54">
         <v>114.3640649112266</v>
       </c>
-      <c r="Q54">
+      <c r="U54">
         <v>207.7725166940945</v>
       </c>
     </row>
@@ -1832,6 +2071,9 @@
       <c r="J55">
         <v>0.4376956417077992</v>
       </c>
+      <c r="K55">
+        <v>85.17601774663507</v>
+      </c>
       <c r="L55">
         <v>1242.110744629077</v>
       </c>
@@ -1839,15 +2081,27 @@
         <v>492.1784768949352</v>
       </c>
       <c r="N55">
+        <v>1734.289221524012</v>
+      </c>
+      <c r="O55">
+        <v>2.523699842515114</v>
+      </c>
+      <c r="P55">
+        <v>0.7162073829517133</v>
+      </c>
+      <c r="Q55">
+        <v>0.2837926170482867</v>
+      </c>
+      <c r="R55">
         <v>1.446934017971433</v>
       </c>
-      <c r="O55">
+      <c r="S55">
         <v>149.0753779965259</v>
       </c>
-      <c r="P55">
+      <c r="T55">
         <v>642.7007889094326</v>
       </c>
-      <c r="Q55">
+      <c r="U55">
         <v>1884.811533538509</v>
       </c>
     </row>
@@ -1885,7 +2139,7 @@
         <v>0.3</v>
       </c>
       <c r="K56">
-        <v>82.40000000000001</v>
+        <v>82.36343036487929</v>
       </c>
       <c r="L56">
         <v>149.2605945872251</v>
@@ -1894,15 +2148,27 @@
         <v>287.1046312644772</v>
       </c>
       <c r="N56">
+        <v>436.3652258517023</v>
+      </c>
+      <c r="O56">
+        <v>0.5198822252704383</v>
+      </c>
+      <c r="P56">
+        <v>0.342054283303388</v>
+      </c>
+      <c r="Q56">
+        <v>0.6579457166966121</v>
+      </c>
+      <c r="R56">
         <v>13.46767277458181</v>
       </c>
-      <c r="O56">
+      <c r="S56">
         <v>25.29154541642356</v>
       </c>
-      <c r="P56">
+      <c r="T56">
         <v>325.8638494554826</v>
       </c>
-      <c r="Q56">
+      <c r="U56">
         <v>475.1244440427076</v>
       </c>
     </row>
@@ -1940,7 +2206,7 @@
         <v>0.3</v>
       </c>
       <c r="K57">
-        <v>83.3</v>
+        <v>83.29829174933647</v>
       </c>
       <c r="L57">
         <v>108.2085044392987</v>
@@ -1949,15 +2215,27 @@
         <v>200.1614400667912</v>
       </c>
       <c r="N57">
+        <v>308.3699445060899</v>
+      </c>
+      <c r="O57">
+        <v>0.5406061447359238</v>
+      </c>
+      <c r="P57">
+        <v>0.3509048348165517</v>
+      </c>
+      <c r="Q57">
+        <v>0.6490951651834483</v>
+      </c>
+      <c r="R57">
         <v>9.22080037915854</v>
       </c>
-      <c r="O57">
+      <c r="S57">
         <v>18.65714519110392</v>
       </c>
-      <c r="P57">
+      <c r="T57">
         <v>228.0393856370537</v>
       </c>
-      <c r="Q57">
+      <c r="U57">
         <v>336.2478900763523</v>
       </c>
     </row>
@@ -1995,7 +2273,7 @@
         <v>0.7</v>
       </c>
       <c r="K58">
-        <v>80.40000000000001</v>
+        <v>80.38667696077663</v>
       </c>
     </row>
     <row r="59">
@@ -2032,7 +2310,7 @@
         <v>0.3</v>
       </c>
       <c r="K59">
-        <v>80.90000000000001</v>
+        <v>80.90614636013449</v>
       </c>
       <c r="L59">
         <v>319.2619842419754</v>
@@ -2041,15 +2319,27 @@
         <v>470.0561306618044</v>
       </c>
       <c r="N59">
+        <v>789.3181149037798</v>
+      </c>
+      <c r="O59">
+        <v>0.6791997027939578</v>
+      </c>
+      <c r="P59">
+        <v>0.4044782176079847</v>
+      </c>
+      <c r="Q59">
+        <v>0.5955217823920153</v>
+      </c>
+      <c r="R59">
         <v>22.63818876381558</v>
       </c>
-      <c r="O59">
+      <c r="S59">
         <v>33.71006222228458</v>
       </c>
-      <c r="P59">
+      <c r="T59">
         <v>526.4043816479046</v>
       </c>
-      <c r="Q59">
+      <c r="U59">
         <v>845.66636588988</v>
       </c>
     </row>
@@ -2086,6 +2376,9 @@
       <c r="J60">
         <v>0.3730075302159346</v>
       </c>
+      <c r="K60">
+        <v>84.6831561394489</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2120,6 +2413,9 @@
       <c r="J61">
         <v>0.364803386403864</v>
       </c>
+      <c r="K61">
+        <v>86.49145137964015</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2155,7 +2451,7 @@
         <v>0.2</v>
       </c>
       <c r="K62">
-        <v>81.90000000000001</v>
+        <v>81.93396670752385</v>
       </c>
       <c r="L62">
         <v>119.2050170293892</v>
@@ -2164,15 +2460,27 @@
         <v>118.5539913271754</v>
       </c>
       <c r="N62">
+        <v>237.7590083565646</v>
+      </c>
+      <c r="O62">
+        <v>1.005491385780653</v>
+      </c>
+      <c r="P62">
+        <v>0.5013690873517552</v>
+      </c>
+      <c r="Q62">
+        <v>0.4986309126482447</v>
+      </c>
+      <c r="R62">
         <v>8.860053886094033</v>
       </c>
-      <c r="O62">
+      <c r="S62">
         <v>21.19536877162439</v>
       </c>
-      <c r="P62">
+      <c r="T62">
         <v>148.6094139848939</v>
       </c>
-      <c r="Q62">
+      <c r="U62">
         <v>267.814431014283</v>
       </c>
     </row>
@@ -2210,7 +2518,7 @@
         <v>0.4</v>
       </c>
       <c r="K63">
-        <v>81.90000000000001</v>
+        <v>81.92457729625423</v>
       </c>
       <c r="L63">
         <v>1080.799441566814</v>
@@ -2219,15 +2527,27 @@
         <v>757.7284980690802</v>
       </c>
       <c r="N63">
+        <v>1838.527939635894</v>
+      </c>
+      <c r="O63">
+        <v>1.426367682251644</v>
+      </c>
+      <c r="P63">
+        <v>0.5878613091845956</v>
+      </c>
+      <c r="Q63">
+        <v>0.4121386908154044</v>
+      </c>
+      <c r="R63">
         <v>41.69596586254642</v>
       </c>
-      <c r="O63">
+      <c r="S63">
         <v>127.7161035122102</v>
       </c>
-      <c r="P63">
+      <c r="T63">
         <v>927.1405674438369</v>
       </c>
-      <c r="Q63">
+      <c r="U63">
         <v>2007.940009010651</v>
       </c>
     </row>
@@ -2264,6 +2584,9 @@
       <c r="J64">
         <v>0.406223064431284</v>
       </c>
+      <c r="K64">
+        <v>85.51678000000578</v>
+      </c>
       <c r="L64">
         <v>537.6122147234918</v>
       </c>
@@ -2271,15 +2594,27 @@
         <v>346.7519528385139</v>
       </c>
       <c r="N64">
+        <v>884.3641675620056</v>
+      </c>
+      <c r="O64">
+        <v>1.55042303387939</v>
+      </c>
+      <c r="P64">
+        <v>0.6079081835773249</v>
+      </c>
+      <c r="Q64">
+        <v>0.3920918164226752</v>
+      </c>
+      <c r="R64">
         <v>3.142217394796511</v>
       </c>
-      <c r="O64">
+      <c r="S64">
         <v>91.9981958532658</v>
       </c>
-      <c r="P64">
+      <c r="T64">
         <v>441.8923660865762</v>
       </c>
-      <c r="Q64">
+      <c r="U64">
         <v>979.5045808100679</v>
       </c>
     </row>
@@ -2327,7 +2662,7 @@
         <v>0.4</v>
       </c>
       <c r="K66">
-        <v>75.09999999999999</v>
+        <v>75.13970681872178</v>
       </c>
       <c r="L66">
         <v>1238.812646965589</v>
@@ -2336,15 +2671,27 @@
         <v>767.0442976352003</v>
       </c>
       <c r="N66">
+        <v>2005.85694460079</v>
+      </c>
+      <c r="O66">
+        <v>1.615047071968141</v>
+      </c>
+      <c r="P66">
+        <v>0.617597705708839</v>
+      </c>
+      <c r="Q66">
+        <v>0.3824022942911611</v>
+      </c>
+      <c r="R66">
         <v>161.0110656711868</v>
       </c>
-      <c r="O66">
+      <c r="S66">
         <v>139.0814770140362</v>
       </c>
-      <c r="P66">
+      <c r="T66">
         <v>1067.136840320423</v>
       </c>
-      <c r="Q66">
+      <c r="U66">
         <v>2305.949487286013</v>
       </c>
     </row>
@@ -2382,7 +2729,7 @@
         <v>0.3</v>
       </c>
       <c r="K67">
-        <v>83.3</v>
+        <v>83.25024583372587</v>
       </c>
       <c r="L67">
         <v>125.7062017538167</v>
@@ -2391,15 +2738,27 @@
         <v>247.3819592530251</v>
       </c>
       <c r="N67">
+        <v>373.0881610068418</v>
+      </c>
+      <c r="O67">
+        <v>0.5081461968099419</v>
+      </c>
+      <c r="P67">
+        <v>0.3369343090774501</v>
+      </c>
+      <c r="Q67">
+        <v>0.6630656909225499</v>
+      </c>
+      <c r="R67">
         <v>16.88478839957311</v>
       </c>
-      <c r="O67">
+      <c r="S67">
         <v>26.51749229071363</v>
       </c>
-      <c r="P67">
+      <c r="T67">
         <v>290.7842399433118</v>
       </c>
-      <c r="Q67">
+      <c r="U67">
         <v>416.4904416971285</v>
       </c>
     </row>
@@ -2437,7 +2796,7 @@
         <v>0.5</v>
       </c>
       <c r="K68">
-        <v>83.8</v>
+        <v>83.84311113065209</v>
       </c>
       <c r="L68">
         <v>188.8034738531314</v>
@@ -2446,15 +2805,27 @@
         <v>316.5630527993579</v>
       </c>
       <c r="N68">
+        <v>505.3665266524894</v>
+      </c>
+      <c r="O68">
+        <v>0.5964166449102249</v>
+      </c>
+      <c r="P68">
+        <v>0.3735971100099402</v>
+      </c>
+      <c r="Q68">
+        <v>0.6264028899900598</v>
+      </c>
+      <c r="R68">
         <v>23.49144195168568</v>
       </c>
-      <c r="O68">
+      <c r="S68">
         <v>41.60445188792254</v>
       </c>
-      <c r="P68">
+      <c r="T68">
         <v>381.6589466389661</v>
       </c>
-      <c r="Q68">
+      <c r="U68">
         <v>570.4624204920976</v>
       </c>
     </row>
@@ -2512,7 +2883,7 @@
         <v>0.3</v>
       </c>
       <c r="K71">
-        <v>80.7</v>
+        <v>80.69340422187776</v>
       </c>
       <c r="L71">
         <v>436.1775581982297</v>
@@ -2521,15 +2892,27 @@
         <v>335.1272482967705</v>
       </c>
       <c r="N71">
+        <v>771.3048064950002</v>
+      </c>
+      <c r="O71">
+        <v>1.301528181951873</v>
+      </c>
+      <c r="P71">
+        <v>0.5655060807676389</v>
+      </c>
+      <c r="Q71">
+        <v>0.4344939192323611</v>
+      </c>
+      <c r="R71">
         <v>21.41954507666827</v>
       </c>
-      <c r="O71">
+      <c r="S71">
         <v>58.49464387039117</v>
       </c>
-      <c r="P71">
+      <c r="T71">
         <v>415.0414372438299</v>
       </c>
-      <c r="Q71">
+      <c r="U71">
         <v>851.2189954420597</v>
       </c>
     </row>
@@ -2566,6 +2949,9 @@
       <c r="J72">
         <v>0.4157705272191733</v>
       </c>
+      <c r="K72">
+        <v>88.03143954239604</v>
+      </c>
       <c r="L72">
         <v>248.6110803478668</v>
       </c>
@@ -2573,15 +2959,27 @@
         <v>247.7324332107889</v>
       </c>
       <c r="N72">
+        <v>496.3435135586557</v>
+      </c>
+      <c r="O72">
+        <v>1.003546758596321</v>
+      </c>
+      <c r="P72">
+        <v>0.5008851199956037</v>
+      </c>
+      <c r="Q72">
+        <v>0.4991148800043962</v>
+      </c>
+      <c r="R72">
         <v>3.004664047892371</v>
       </c>
-      <c r="O72">
+      <c r="S72">
         <v>58.48890673820321</v>
       </c>
-      <c r="P72">
+      <c r="T72">
         <v>309.2260039968845</v>
       </c>
-      <c r="Q72">
+      <c r="U72">
         <v>557.8370843447514</v>
       </c>
     </row>
@@ -2629,7 +3027,7 @@
         <v>0.2</v>
       </c>
       <c r="K74">
-        <v>81.7</v>
+        <v>81.71027956554434</v>
       </c>
       <c r="L74">
         <v>395.4368497298076</v>
@@ -2638,15 +3036,27 @@
         <v>498.7511441204631</v>
       </c>
       <c r="N74">
+        <v>894.1879938502707</v>
+      </c>
+      <c r="O74">
+        <v>0.7928540202692707</v>
+      </c>
+      <c r="P74">
+        <v>0.4422301042391567</v>
+      </c>
+      <c r="Q74">
+        <v>0.5577698957608433</v>
+      </c>
+      <c r="R74">
         <v>35.0488898029394</v>
       </c>
-      <c r="O74">
+      <c r="S74">
         <v>59.09808394331837</v>
       </c>
-      <c r="P74">
+      <c r="T74">
         <v>592.8981178667208</v>
       </c>
-      <c r="Q74">
+      <c r="U74">
         <v>988.3349675965284</v>
       </c>
     </row>
@@ -2683,6 +3093,9 @@
       <c r="J75">
         <v>0.3508037605909318</v>
       </c>
+      <c r="K75">
+        <v>71.17865078976575</v>
+      </c>
       <c r="L75">
         <v>632.2048538518014</v>
       </c>
@@ -2690,15 +3103,27 @@
         <v>1418.731286843074</v>
       </c>
       <c r="N75">
+        <v>2050.936140694876</v>
+      </c>
+      <c r="O75">
+        <v>0.4456128230304753</v>
+      </c>
+      <c r="P75">
+        <v>0.3082518471967658</v>
+      </c>
+      <c r="Q75">
+        <v>0.6917481528032342</v>
+      </c>
+      <c r="R75">
         <v>4.544769815961037</v>
       </c>
-      <c r="O75">
+      <c r="S75">
         <v>176.7192515864101</v>
       </c>
-      <c r="P75">
+      <c r="T75">
         <v>1599.995308245446</v>
       </c>
-      <c r="Q75">
+      <c r="U75">
         <v>2232.200162097247</v>
       </c>
     </row>
@@ -2735,6 +3160,9 @@
       <c r="J76">
         <v>0.3397364627618759</v>
       </c>
+      <c r="K76">
+        <v>85.85483043161921</v>
+      </c>
       <c r="L76">
         <v>925.1580749484533</v>
       </c>
@@ -2742,15 +3170,27 @@
         <v>415.0910313232905</v>
       </c>
       <c r="N76">
+        <v>1340.249106271744</v>
+      </c>
+      <c r="O76">
+        <v>2.22880767141389</v>
+      </c>
+      <c r="P76">
+        <v>0.6902881491352189</v>
+      </c>
+      <c r="Q76">
+        <v>0.3097118508647811</v>
+      </c>
+      <c r="R76">
         <v>2.233740362207405</v>
       </c>
-      <c r="O76">
+      <c r="S76">
         <v>67.31802669156841</v>
       </c>
-      <c r="P76">
+      <c r="T76">
         <v>484.6427983770662</v>
       </c>
-      <c r="Q76">
+      <c r="U76">
         <v>1409.800873325519</v>
       </c>
     </row>
@@ -2787,6 +3227,9 @@
       <c r="J77">
         <v>0.4823524313678453</v>
       </c>
+      <c r="K77">
+        <v>83.90693610973571</v>
+      </c>
       <c r="L77">
         <v>588.7420144071734</v>
       </c>
@@ -2794,15 +3237,27 @@
         <v>618.2527532390445</v>
       </c>
       <c r="N77">
+        <v>1206.994767646218</v>
+      </c>
+      <c r="O77">
+        <v>0.9522675173264277</v>
+      </c>
+      <c r="P77">
+        <v>0.4877751173315272</v>
+      </c>
+      <c r="Q77">
+        <v>0.5122248826684728</v>
+      </c>
+      <c r="R77">
         <v>4.266953932472603</v>
       </c>
-      <c r="O77">
+      <c r="S77">
         <v>100.7814358360728</v>
       </c>
-      <c r="P77">
+      <c r="T77">
         <v>723.3011430075899</v>
       </c>
-      <c r="Q77">
+      <c r="U77">
         <v>1312.043157414763</v>
       </c>
     </row>
@@ -2839,6 +3294,9 @@
       <c r="J78">
         <v>0.3583679266761579</v>
       </c>
+      <c r="K78">
+        <v>89.32140376683485</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2900,15 +3358,27 @@
         <v>500.8776483223987</v>
       </c>
       <c r="N81">
+        <v>1423.386444624371</v>
+      </c>
+      <c r="O81">
+        <v>1.84178471407489</v>
+      </c>
+      <c r="P81">
+        <v>0.6481084597833308</v>
+      </c>
+      <c r="Q81">
+        <v>0.3518915402166692</v>
+      </c>
+      <c r="R81">
         <v>51.25126659555103</v>
       </c>
-      <c r="O81">
+      <c r="S81">
         <v>76.80678304468228</v>
       </c>
-      <c r="P81">
+      <c r="T81">
         <v>628.935697962632</v>
       </c>
-      <c r="Q81">
+      <c r="U81">
         <v>1551.444494264604</v>
       </c>
     </row>
@@ -2956,7 +3426,7 @@
         <v>0.5</v>
       </c>
       <c r="K83">
-        <v>83.40000000000001</v>
+        <v>83.37326917124977</v>
       </c>
     </row>
     <row r="84">
@@ -2999,15 +3469,27 @@
         <v>143.0708598629755</v>
       </c>
       <c r="N84">
+        <v>246.223988444746</v>
+      </c>
+      <c r="O84">
+        <v>0.7209932803966115</v>
+      </c>
+      <c r="P84">
+        <v>0.4189402065709722</v>
+      </c>
+      <c r="Q84">
+        <v>0.5810597934290278</v>
+      </c>
+      <c r="R84">
         <v>9.5714507714078</v>
       </c>
-      <c r="O84">
+      <c r="S84">
         <v>20.86552252530479</v>
       </c>
-      <c r="P84">
+      <c r="T84">
         <v>173.507833159688</v>
       </c>
-      <c r="Q84">
+      <c r="U84">
         <v>276.6609617414586</v>
       </c>
     </row>
@@ -3021,7 +3503,7 @@
         <v>38</v>
       </c>
       <c r="K85">
-        <v>74.90000000000001</v>
+        <v>74.88514529529995</v>
       </c>
       <c r="L85">
         <v>222.3081090710803</v>
@@ -3030,15 +3512,27 @@
         <v>437.2386585101507</v>
       </c>
       <c r="N85">
+        <v>659.5467675812309</v>
+      </c>
+      <c r="O85">
+        <v>0.5084365363039354</v>
+      </c>
+      <c r="P85">
+        <v>0.3370619340404855</v>
+      </c>
+      <c r="Q85">
+        <v>0.6629380659595145</v>
+      </c>
+      <c r="R85">
         <v>23.48781191572468</v>
       </c>
-      <c r="O85">
+      <c r="S85">
         <v>28.12140748375579</v>
       </c>
-      <c r="P85">
+      <c r="T85">
         <v>488.8478779096312</v>
       </c>
-      <c r="Q85">
+      <c r="U85">
         <v>711.1559869807114</v>
       </c>
     </row>
@@ -3076,7 +3570,7 @@
         <v>0.5</v>
       </c>
       <c r="K86">
-        <v>78</v>
+        <v>77.97157498879098</v>
       </c>
       <c r="L86">
         <v>318.9798722062764</v>
@@ -3085,15 +3579,27 @@
         <v>397.9596050562783</v>
       </c>
       <c r="N86">
+        <v>716.9394772625546</v>
+      </c>
+      <c r="O86">
+        <v>0.8015383173404425</v>
+      </c>
+      <c r="P86">
+        <v>0.4449188283287417</v>
+      </c>
+      <c r="Q86">
+        <v>0.5550811716712584</v>
+      </c>
+      <c r="R86">
         <v>28.62666013853691</v>
       </c>
-      <c r="O86">
+      <c r="S86">
         <v>43.06155062407122</v>
       </c>
-      <c r="P86">
+      <c r="T86">
         <v>469.6478158188864</v>
       </c>
-      <c r="Q86">
+      <c r="U86">
         <v>788.6276880251627</v>
       </c>
     </row>
@@ -3130,6 +3636,9 @@
       <c r="J87">
         <v>0.4437881428156286</v>
       </c>
+      <c r="K87">
+        <v>73.51730294240244</v>
+      </c>
       <c r="L87">
         <v>635.9031448602332</v>
       </c>
@@ -3137,15 +3646,27 @@
         <v>798.1851680740846</v>
       </c>
       <c r="N87">
+        <v>1434.088312934318</v>
+      </c>
+      <c r="O87">
+        <v>0.7966862456171461</v>
+      </c>
+      <c r="P87">
+        <v>0.4434197943912523</v>
+      </c>
+      <c r="Q87">
+        <v>0.5565802056087475</v>
+      </c>
+      <c r="R87">
         <v>10.7888904046263</v>
       </c>
-      <c r="O87">
+      <c r="S87">
         <v>137.0269991710594</v>
       </c>
-      <c r="P87">
+      <c r="T87">
         <v>946.0010576497702</v>
       </c>
-      <c r="Q87">
+      <c r="U87">
         <v>1581.904202510003</v>
       </c>
     </row>
@@ -3183,7 +3704,7 @@
         <v>0.3</v>
       </c>
       <c r="K88">
-        <v>73.40000000000001</v>
+        <v>73.35471259057127</v>
       </c>
       <c r="L88">
         <v>1264.528713979829</v>
@@ -3192,15 +3713,27 @@
         <v>1163.66869592662</v>
       </c>
       <c r="N88">
+        <v>2428.197409906449</v>
+      </c>
+      <c r="O88">
+        <v>1.086674169723965</v>
+      </c>
+      <c r="P88">
+        <v>0.5207684963425387</v>
+      </c>
+      <c r="Q88">
+        <v>0.4792315036574612</v>
+      </c>
+      <c r="R88">
         <v>55.09558297690605</v>
       </c>
-      <c r="O88">
+      <c r="S88">
         <v>154.8073500892277</v>
       </c>
-      <c r="P88">
+      <c r="T88">
         <v>1373.571628992754</v>
       </c>
-      <c r="Q88">
+      <c r="U88">
         <v>2638.100342972583</v>
       </c>
     </row>
@@ -3238,7 +3771,7 @@
         <v>0.3</v>
       </c>
       <c r="K89">
-        <v>64.90000000000001</v>
+        <v>64.9478057823052</v>
       </c>
       <c r="L89">
         <v>761.8467170278481</v>
@@ -3247,15 +3780,27 @@
         <v>1235.233177660139</v>
       </c>
       <c r="N89">
+        <v>1997.079894687987</v>
+      </c>
+      <c r="O89">
+        <v>0.6167634830461639</v>
+      </c>
+      <c r="P89">
+        <v>0.3814803398974055</v>
+      </c>
+      <c r="Q89">
+        <v>0.6185196601025944</v>
+      </c>
+      <c r="R89">
         <v>57.3785355537061</v>
       </c>
-      <c r="O89">
+      <c r="S89">
         <v>105.0862634854969</v>
       </c>
-      <c r="P89">
+      <c r="T89">
         <v>1397.697976699342</v>
       </c>
-      <c r="Q89">
+      <c r="U89">
         <v>2159.54469372719</v>
       </c>
     </row>
@@ -3309,15 +3854,27 @@
         <v>1076.573015967258</v>
       </c>
       <c r="N91">
+        <v>1621.213372599727</v>
+      </c>
+      <c r="O91">
+        <v>0.5059019207750919</v>
+      </c>
+      <c r="P91">
+        <v>0.3359461288917825</v>
+      </c>
+      <c r="Q91">
+        <v>0.6640538711082175</v>
+      </c>
+      <c r="R91">
         <v>66.9596640177172</v>
       </c>
-      <c r="O91">
+      <c r="S91">
         <v>111.450560677828</v>
       </c>
-      <c r="P91">
+      <c r="T91">
         <v>1254.983240662803</v>
       </c>
-      <c r="Q91">
+      <c r="U91">
         <v>1799.623597295272</v>
       </c>
     </row>
@@ -3354,6 +3911,9 @@
       <c r="J92">
         <v>0.3499625518373096</v>
       </c>
+      <c r="K92">
+        <v>84.09116440092386</v>
+      </c>
       <c r="L92">
         <v>1117.08801398357</v>
       </c>
@@ -3361,15 +3921,27 @@
         <v>465.5776603652828</v>
       </c>
       <c r="N92">
+        <v>1582.665674348853</v>
+      </c>
+      <c r="O92">
+        <v>2.399359138295264</v>
+      </c>
+      <c r="P92">
+        <v>0.7058269046260621</v>
+      </c>
+      <c r="Q92">
+        <v>0.2941730953739379</v>
+      </c>
+      <c r="R92">
         <v>2.761306193688941</v>
       </c>
-      <c r="O92">
+      <c r="S92">
         <v>142.4007417572687</v>
       </c>
-      <c r="P92">
+      <c r="T92">
         <v>610.7397083162405</v>
       </c>
-      <c r="Q92">
+      <c r="U92">
         <v>1727.82772229981</v>
       </c>
     </row>
@@ -3417,7 +3989,7 @@
         <v>0.3</v>
       </c>
       <c r="K94">
-        <v>74.7</v>
+        <v>74.73847464224437</v>
       </c>
       <c r="L94">
         <v>974.521258627761</v>
@@ -3426,15 +3998,27 @@
         <v>1115.353358412675</v>
       </c>
       <c r="N94">
+        <v>2089.874617040437</v>
+      </c>
+      <c r="O94">
+        <v>0.8737331996871909</v>
+      </c>
+      <c r="P94">
+        <v>0.4663060887393443</v>
+      </c>
+      <c r="Q94">
+        <v>0.5336939112606556</v>
+      </c>
+      <c r="R94">
         <v>64.81564692008988</v>
       </c>
-      <c r="O94">
+      <c r="S94">
         <v>124.0443278498251</v>
       </c>
-      <c r="P94">
+      <c r="T94">
         <v>1304.21333318259</v>
       </c>
-      <c r="Q94">
+      <c r="U94">
         <v>2278.734591810352</v>
       </c>
     </row>
@@ -3472,7 +4056,7 @@
         <v>0.3</v>
       </c>
       <c r="K95">
-        <v>77</v>
+        <v>77.04268446920611</v>
       </c>
       <c r="L95">
         <v>1605.323015044763</v>
@@ -3481,15 +4065,27 @@
         <v>1238.541805810417</v>
       </c>
       <c r="N95">
+        <v>2843.864820855181</v>
+      </c>
+      <c r="O95">
+        <v>1.296139546936286</v>
+      </c>
+      <c r="P95">
+        <v>0.5644864000821338</v>
+      </c>
+      <c r="Q95">
+        <v>0.4355135999178661</v>
+      </c>
+      <c r="R95">
         <v>181.9654603243459</v>
       </c>
-      <c r="O95">
+      <c r="S95">
         <v>194.3276438427655</v>
       </c>
-      <c r="P95">
+      <c r="T95">
         <v>1614.834909977529</v>
       </c>
-      <c r="Q95">
+      <c r="U95">
         <v>3220.157925022292</v>
       </c>
     </row>
@@ -3546,6 +4142,9 @@
       <c r="J98">
         <v>0.4184506415061264</v>
       </c>
+      <c r="K98">
+        <v>77.64924630053648</v>
+      </c>
       <c r="L98">
         <v>343.9948503936504</v>
       </c>
@@ -3553,15 +4152,27 @@
         <v>354.0410202932833</v>
       </c>
       <c r="N98">
+        <v>698.0358706869337</v>
+      </c>
+      <c r="O98">
+        <v>0.9716242770645311</v>
+      </c>
+      <c r="P98">
+        <v>0.4928039730323984</v>
+      </c>
+      <c r="Q98">
+        <v>0.5071960269676016</v>
+      </c>
+      <c r="R98">
         <v>2.843204582135876</v>
       </c>
-      <c r="O98">
+      <c r="S98">
         <v>46.46533508590285</v>
       </c>
-      <c r="P98">
+      <c r="T98">
         <v>403.349559961322</v>
       </c>
-      <c r="Q98">
+      <c r="U98">
         <v>747.3444103549724</v>
       </c>
     </row>
@@ -3608,6 +4219,9 @@
       <c r="J100">
         <v>0.3139688856768904</v>
       </c>
+      <c r="K100">
+        <v>86.24933439132818</v>
+      </c>
       <c r="L100">
         <v>476.0304210375268</v>
       </c>
@@ -3615,15 +4229,27 @@
         <v>503.0929384998295</v>
       </c>
       <c r="N100">
+        <v>979.1233595373562</v>
+      </c>
+      <c r="O100">
+        <v>0.9462077175183569</v>
+      </c>
+      <c r="P100">
+        <v>0.4861802309184565</v>
+      </c>
+      <c r="Q100">
+        <v>0.5138197690815436</v>
+      </c>
+      <c r="R100">
         <v>6.013098565098522</v>
       </c>
-      <c r="O100">
+      <c r="S100">
         <v>96.09673351257763</v>
       </c>
-      <c r="P100">
+      <c r="T100">
         <v>605.2027705775057</v>
       </c>
-      <c r="Q100">
+      <c r="U100">
         <v>1081.233191615032</v>
       </c>
     </row>
@@ -3681,7 +4307,7 @@
         <v>0.4</v>
       </c>
       <c r="K103">
-        <v>75.5</v>
+        <v>75.50721533761069</v>
       </c>
       <c r="L103">
         <v>128.2502881426015</v>
@@ -3690,15 +4316,27 @@
         <v>306.2669023359975</v>
       </c>
       <c r="N103">
+        <v>434.517190478599</v>
+      </c>
+      <c r="O103">
+        <v>0.4187533395361847</v>
+      </c>
+      <c r="P103">
+        <v>0.2951558441251546</v>
+      </c>
+      <c r="Q103">
+        <v>0.7048441558748453</v>
+      </c>
+      <c r="R103">
         <v>10.3383152295418</v>
       </c>
-      <c r="O103">
+      <c r="S103">
         <v>26.00824753386626</v>
       </c>
-      <c r="P103">
+      <c r="T103">
         <v>342.6134650994056</v>
       </c>
-      <c r="Q103">
+      <c r="U103">
         <v>470.8637532420071</v>
       </c>
     </row>
@@ -3746,7 +4384,7 @@
         <v>0.4</v>
       </c>
       <c r="K105">
-        <v>82</v>
+        <v>81.96854996125444</v>
       </c>
       <c r="L105">
         <v>62.4727055258625</v>
@@ -3755,15 +4393,27 @@
         <v>108.4154497901999</v>
       </c>
       <c r="N105">
+        <v>170.8881553160624</v>
+      </c>
+      <c r="O105">
+        <v>0.5762343434146752</v>
+      </c>
+      <c r="P105">
+        <v>0.3655765691327026</v>
+      </c>
+      <c r="Q105">
+        <v>0.6344234308672974</v>
+      </c>
+      <c r="R105">
         <v>8.425148402608997</v>
       </c>
-      <c r="O105">
+      <c r="S105">
         <v>19.39190872873992</v>
       </c>
-      <c r="P105">
+      <c r="T105">
         <v>136.2325069215488</v>
       </c>
-      <c r="Q105">
+      <c r="U105">
         <v>198.7052124474113</v>
       </c>
     </row>
@@ -3801,7 +4451,7 @@
         <v>0.4</v>
       </c>
       <c r="K106">
-        <v>78.40000000000001</v>
+        <v>78.42840311093316</v>
       </c>
       <c r="L106">
         <v>393.329946872944</v>
@@ -3810,15 +4460,27 @@
         <v>757.8738801438984</v>
       </c>
       <c r="N106">
+        <v>1151.203827016842</v>
+      </c>
+      <c r="O106">
+        <v>0.518991295488719</v>
+      </c>
+      <c r="P106">
+        <v>0.3416683802139493</v>
+      </c>
+      <c r="Q106">
+        <v>0.6583316197860508</v>
+      </c>
+      <c r="R106">
         <v>29.90883125862541</v>
       </c>
-      <c r="O106">
+      <c r="S106">
         <v>41.55219056921599</v>
       </c>
-      <c r="P106">
+      <c r="T106">
         <v>829.3349019717398</v>
       </c>
-      <c r="Q106">
+      <c r="U106">
         <v>1222.664848844684</v>
       </c>
     </row>
@@ -3865,6 +4527,9 @@
       <c r="J108">
         <v>0.3844029656063214</v>
       </c>
+      <c r="K108">
+        <v>87.58076444329757</v>
+      </c>
       <c r="L108">
         <v>133.7500103793838</v>
       </c>
@@ -3872,15 +4537,27 @@
         <v>125.2418701360886</v>
       </c>
       <c r="N108">
+        <v>258.9918805154724</v>
+      </c>
+      <c r="O108">
+        <v>1.067933672932624</v>
+      </c>
+      <c r="P108">
+        <v>0.516425496093471</v>
+      </c>
+      <c r="Q108">
+        <v>0.483574503906529</v>
+      </c>
+      <c r="R108">
         <v>1.912063272290525</v>
       </c>
-      <c r="O108">
+      <c r="S108">
         <v>20.86143602972172</v>
       </c>
-      <c r="P108">
+      <c r="T108">
         <v>148.0153694381008</v>
       </c>
-      <c r="Q108">
+      <c r="U108">
         <v>281.7653798174847</v>
       </c>
     </row>
@@ -3918,7 +4595,7 @@
         <v>0.5</v>
       </c>
       <c r="K109">
-        <v>54</v>
+        <v>53.95114265997569</v>
       </c>
       <c r="L109">
         <v>155.1709729785362</v>
@@ -3927,15 +4604,27 @@
         <v>183.8001147762915</v>
       </c>
       <c r="N109">
+        <v>338.9710877548277</v>
+      </c>
+      <c r="O109">
+        <v>0.8442376282920135</v>
+      </c>
+      <c r="P109">
+        <v>0.457770525522722</v>
+      </c>
+      <c r="Q109">
+        <v>0.5422294744772779</v>
+      </c>
+      <c r="R109">
         <v>50.86021346422319</v>
       </c>
-      <c r="O109">
+      <c r="S109">
         <v>59.36805660323616</v>
       </c>
-      <c r="P109">
+      <c r="T109">
         <v>294.0283848437509</v>
       </c>
-      <c r="Q109">
+      <c r="U109">
         <v>449.1993578222871</v>
       </c>
     </row>
@@ -3972,6 +4661,9 @@
       <c r="J110">
         <v>0.4831195226435</v>
       </c>
+      <c r="K110">
+        <v>84.90514955773061</v>
+      </c>
       <c r="L110">
         <v>104.697522260356</v>
       </c>
@@ -3979,15 +4671,27 @@
         <v>194.6851077089309</v>
       </c>
       <c r="N110">
+        <v>299.3826299692869</v>
+      </c>
+      <c r="O110">
+        <v>0.5377787931108056</v>
+      </c>
+      <c r="P110">
+        <v>0.3497114120184486</v>
+      </c>
+      <c r="Q110">
+        <v>0.6502885879815514</v>
+      </c>
+      <c r="R110">
         <v>3.067443486022155</v>
       </c>
-      <c r="O110">
+      <c r="S110">
         <v>24.17564783159253</v>
       </c>
-      <c r="P110">
+      <c r="T110">
         <v>221.9281990265456</v>
       </c>
-      <c r="Q110">
+      <c r="U110">
         <v>326.6257212869016</v>
       </c>
     </row>
@@ -4025,7 +4729,7 @@
         <v>0.5</v>
       </c>
       <c r="K111">
-        <v>71.5</v>
+        <v>71.46650790709283</v>
       </c>
       <c r="L111">
         <v>171.4608520356959</v>
@@ -4034,15 +4738,27 @@
         <v>311.3612261772755</v>
       </c>
       <c r="N111">
+        <v>482.8220782129714</v>
+      </c>
+      <c r="O111">
+        <v>0.550681451704181</v>
+      </c>
+      <c r="P111">
+        <v>0.355122227778625</v>
+      </c>
+      <c r="Q111">
+        <v>0.6448777722213751</v>
+      </c>
+      <c r="R111">
         <v>10.78675173539649</v>
       </c>
-      <c r="O111">
+      <c r="S111">
         <v>58.21509765819793</v>
       </c>
-      <c r="P111">
+      <c r="T111">
         <v>380.3630755708699</v>
       </c>
-      <c r="Q111">
+      <c r="U111">
         <v>551.8239276065658</v>
       </c>
     </row>
@@ -4079,6 +4795,9 @@
       <c r="J112">
         <v>0.4880453355397287</v>
       </c>
+      <c r="K112">
+        <v>84.95630598675744</v>
+      </c>
       <c r="L112">
         <v>199.9991211471886</v>
       </c>
@@ -4086,15 +4805,27 @@
         <v>277.7545181624432</v>
       </c>
       <c r="N112">
+        <v>477.7536393096318</v>
+      </c>
+      <c r="O112">
+        <v>0.720057129836571</v>
+      </c>
+      <c r="P112">
+        <v>0.4186239615802682</v>
+      </c>
+      <c r="Q112">
+        <v>0.5813760384197318</v>
+      </c>
+      <c r="R112">
         <v>3.178758996931944</v>
       </c>
-      <c r="O112">
+      <c r="S112">
         <v>37.39818652947594</v>
       </c>
-      <c r="P112">
+      <c r="T112">
         <v>318.3314636888511</v>
       </c>
-      <c r="Q112">
+      <c r="U112">
         <v>518.3305848360397</v>
       </c>
     </row>
@@ -4132,7 +4863,7 @@
         <v>0.5</v>
       </c>
       <c r="K113">
-        <v>73.90000000000001</v>
+        <v>73.87335322453352</v>
       </c>
       <c r="L113">
         <v>1463.574835474183</v>
@@ -4141,15 +4872,27 @@
         <v>1811.170828385713</v>
       </c>
       <c r="N113">
+        <v>3274.745663859896</v>
+      </c>
+      <c r="O113">
+        <v>0.8080821601895274</v>
+      </c>
+      <c r="P113">
+        <v>0.446927787896996</v>
+      </c>
+      <c r="Q113">
+        <v>0.5530722121030041</v>
+      </c>
+      <c r="R113">
         <v>101.6863865708629</v>
       </c>
-      <c r="O113">
+      <c r="S113">
         <v>242.343935224454</v>
       </c>
-      <c r="P113">
+      <c r="T113">
         <v>2155.20115018103</v>
       </c>
-      <c r="Q113">
+      <c r="U113">
         <v>3618.775985655212</v>
       </c>
     </row>
@@ -4197,7 +4940,7 @@
         <v>0.3</v>
       </c>
       <c r="K115">
-        <v>79.3</v>
+        <v>79.3134816047378</v>
       </c>
       <c r="L115">
         <v>488.774076195937</v>
@@ -4206,15 +4949,27 @@
         <v>538.4528237337443</v>
       </c>
       <c r="N115">
+        <v>1027.226899929681</v>
+      </c>
+      <c r="O115">
+        <v>0.9077379756441346</v>
+      </c>
+      <c r="P115">
+        <v>0.4758189999009917</v>
+      </c>
+      <c r="Q115">
+        <v>0.5241810000990084</v>
+      </c>
+      <c r="R115">
         <v>22.2573679724291</v>
       </c>
-      <c r="O115">
+      <c r="S115">
         <v>69.87637083393869</v>
       </c>
-      <c r="P115">
+      <c r="T115">
         <v>630.586562540112</v>
       </c>
-      <c r="Q115">
+      <c r="U115">
         <v>1119.360638736049</v>
       </c>
     </row>
@@ -4251,6 +5006,9 @@
       <c r="J116">
         <v>0.329156798720227</v>
       </c>
+      <c r="K116">
+        <v>82.9039010924046</v>
+      </c>
       <c r="L116">
         <v>73.23603057127377</v>
       </c>
@@ -4258,15 +5016,27 @@
         <v>244.4456129157851</v>
       </c>
       <c r="N116">
+        <v>317.6816434870589</v>
+      </c>
+      <c r="O116">
+        <v>0.2996005111227118</v>
+      </c>
+      <c r="P116">
+        <v>0.2305327741552594</v>
+      </c>
+      <c r="Q116">
+        <v>0.7694672258447406</v>
+      </c>
+      <c r="R116">
         <v>5.011360708394362</v>
       </c>
-      <c r="O116">
+      <c r="S116">
         <v>28.79561169623933</v>
       </c>
-      <c r="P116">
+      <c r="T116">
         <v>278.2525853204188</v>
       </c>
-      <c r="Q116">
+      <c r="U116">
         <v>351.4886158916926</v>
       </c>
     </row>
@@ -4313,6 +5083,9 @@
       <c r="J118">
         <v>0.3561853598264639</v>
       </c>
+      <c r="K118">
+        <v>87.41980182282818</v>
+      </c>
       <c r="L118">
         <v>107.7392087048096</v>
       </c>
@@ -4320,15 +5093,27 @@
         <v>108.2574140974768</v>
       </c>
       <c r="N118">
+        <v>215.9966228022863</v>
+      </c>
+      <c r="O118">
+        <v>0.9952132110582228</v>
+      </c>
+      <c r="P118">
+        <v>0.4988004317244776</v>
+      </c>
+      <c r="Q118">
+        <v>0.5011995682755224</v>
+      </c>
+      <c r="R118">
         <v>1.696498813434979</v>
       </c>
-      <c r="O118">
+      <c r="S118">
         <v>33.51715843895689</v>
       </c>
-      <c r="P118">
+      <c r="T118">
         <v>143.4710713498686</v>
       </c>
-      <c r="Q118">
+      <c r="U118">
         <v>251.2102800546782</v>
       </c>
     </row>
@@ -4366,7 +5151,7 @@
         <v>0.2</v>
       </c>
       <c r="K119">
-        <v>76.8</v>
+        <v>76.77129243667252</v>
       </c>
       <c r="L119">
         <v>285.6451777256668</v>
@@ -4375,15 +5160,27 @@
         <v>407.4620364394208</v>
       </c>
       <c r="N119">
+        <v>693.1072141650876</v>
+      </c>
+      <c r="O119">
+        <v>0.7010350711976943</v>
+      </c>
+      <c r="P119">
+        <v>0.4121226440699411</v>
+      </c>
+      <c r="Q119">
+        <v>0.587877355930059</v>
+      </c>
+      <c r="R119">
         <v>18.3059939745396</v>
       </c>
-      <c r="O119">
+      <c r="S119">
         <v>31.8912556256901</v>
       </c>
-      <c r="P119">
+      <c r="T119">
         <v>457.6592860396505</v>
       </c>
-      <c r="Q119">
+      <c r="U119">
         <v>743.3044637653172</v>
       </c>
     </row>
@@ -4440,6 +5237,9 @@
       <c r="J122">
         <v>0.272844146355717</v>
       </c>
+      <c r="K122">
+        <v>79.63292836112883</v>
+      </c>
       <c r="L122">
         <v>539.5318613391844</v>
       </c>
@@ -4447,15 +5247,27 @@
         <v>981.9810635305923</v>
       </c>
       <c r="N122">
+        <v>1521.512924869777</v>
+      </c>
+      <c r="O122">
+        <v>0.5494320424055469</v>
+      </c>
+      <c r="P122">
+        <v>0.3546022202771376</v>
+      </c>
+      <c r="Q122">
+        <v>0.6453977797228625</v>
+      </c>
+      <c r="R122">
         <v>4.890769716441704</v>
       </c>
-      <c r="O122">
+      <c r="S122">
         <v>120.9950825119892</v>
       </c>
-      <c r="P122">
+      <c r="T122">
         <v>1107.866915759023</v>
       </c>
-      <c r="Q122">
+      <c r="U122">
         <v>1647.398777098208</v>
       </c>
     </row>
@@ -4493,7 +5305,7 @@
         <v>0.3</v>
       </c>
       <c r="K123">
-        <v>81.5</v>
+        <v>81.48633144095425</v>
       </c>
     </row>
     <row r="124">
@@ -4530,7 +5342,7 @@
         <v>0.4</v>
       </c>
       <c r="K124">
-        <v>81.5</v>
+        <v>81.51817590978958</v>
       </c>
       <c r="L124">
         <v>477.4502570224365</v>
@@ -4539,15 +5351,27 @@
         <v>404.9389854603876</v>
       </c>
       <c r="N124">
+        <v>882.3892424828241</v>
+      </c>
+      <c r="O124">
+        <v>1.179067153733317</v>
+      </c>
+      <c r="P124">
+        <v>0.541088030129436</v>
+      </c>
+      <c r="Q124">
+        <v>0.458911969870564</v>
+      </c>
+      <c r="R124">
         <v>29.99593628337087</v>
       </c>
-      <c r="O124">
+      <c r="S124">
         <v>38.71768280466419</v>
       </c>
-      <c r="P124">
+      <c r="T124">
         <v>473.6526045484227</v>
       </c>
-      <c r="Q124">
+      <c r="U124">
         <v>951.1028615708591</v>
       </c>
     </row>
@@ -4615,7 +5439,7 @@
         <v>0.4</v>
       </c>
       <c r="K128">
-        <v>83.2</v>
+        <v>83.24130247009533</v>
       </c>
       <c r="L128">
         <v>109.8127014392606</v>
@@ -4624,15 +5448,27 @@
         <v>206.680841306193</v>
       </c>
       <c r="N128">
+        <v>316.4935427454536</v>
+      </c>
+      <c r="O128">
+        <v>0.5313153398508551</v>
+      </c>
+      <c r="P128">
+        <v>0.3469666410463853</v>
+      </c>
+      <c r="Q128">
+        <v>0.6530333589536148</v>
+      </c>
+      <c r="R128">
         <v>13.30634257275144</v>
       </c>
-      <c r="O128">
+      <c r="S128">
         <v>19.85636563226463</v>
       </c>
-      <c r="P128">
+      <c r="T128">
         <v>239.8435495112091</v>
       </c>
-      <c r="Q128">
+      <c r="U128">
         <v>349.6562509504697</v>
       </c>
     </row>
@@ -4710,7 +5546,7 @@
         <v>0.4</v>
       </c>
       <c r="K133">
-        <v>82.2</v>
+        <v>82.19098001183036</v>
       </c>
       <c r="L133">
         <v>273.1833777498271</v>
@@ -4719,15 +5555,27 @@
         <v>284.8703044563161</v>
       </c>
       <c r="N133">
+        <v>558.0536822061432</v>
+      </c>
+      <c r="O133">
+        <v>0.9589745700985091</v>
+      </c>
+      <c r="P133">
+        <v>0.4895288508264229</v>
+      </c>
+      <c r="Q133">
+        <v>0.5104711491735771</v>
+      </c>
+      <c r="R133">
         <v>18.4477663734207</v>
       </c>
-      <c r="O133">
+      <c r="S133">
         <v>46.7812285807698</v>
       </c>
-      <c r="P133">
+      <c r="T133">
         <v>350.0992994105065</v>
       </c>
-      <c r="Q133">
+      <c r="U133">
         <v>623.2826771603337</v>
       </c>
     </row>
@@ -4775,7 +5623,7 @@
         <v>0.7</v>
       </c>
       <c r="K135">
-        <v>85.59999999999999</v>
+        <v>85.59448235071713</v>
       </c>
       <c r="L135">
         <v>188.4472264021882</v>
@@ -4784,15 +5632,27 @@
         <v>259.7718714091473</v>
       </c>
       <c r="N135">
+        <v>448.2190978113356</v>
+      </c>
+      <c r="O135">
+        <v>0.7254335328145636</v>
+      </c>
+      <c r="P135">
+        <v>0.4204355131728668</v>
+      </c>
+      <c r="Q135">
+        <v>0.5795644868271331</v>
+      </c>
+      <c r="R135">
         <v>18.0472033032963</v>
       </c>
-      <c r="O135">
+      <c r="S135">
         <v>58.18729050707613</v>
       </c>
-      <c r="P135">
+      <c r="T135">
         <v>336.0063652195197</v>
       </c>
-      <c r="Q135">
+      <c r="U135">
         <v>524.453591621708</v>
       </c>
     </row>
@@ -4840,7 +5700,7 @@
         <v>0.4</v>
       </c>
       <c r="K137">
-        <v>83.3</v>
+        <v>83.30273554352902</v>
       </c>
       <c r="L137">
         <v>207.6215754263435</v>
@@ -4849,15 +5709,27 @@
         <v>284.5120690169071</v>
       </c>
       <c r="N137">
+        <v>492.1336444432507</v>
+      </c>
+      <c r="O137">
+        <v>0.7297461093434515</v>
+      </c>
+      <c r="P137">
+        <v>0.4218804744821403</v>
+      </c>
+      <c r="Q137">
+        <v>0.5781195255178596</v>
+      </c>
+      <c r="R137">
         <v>12.49889144536523</v>
       </c>
-      <c r="O137">
+      <c r="S137">
         <v>27.95567711026671</v>
       </c>
-      <c r="P137">
+      <c r="T137">
         <v>324.9666375725391</v>
       </c>
-      <c r="Q137">
+      <c r="U137">
         <v>532.5882129988826</v>
       </c>
     </row>
@@ -4915,7 +5787,7 @@
         <v>0.5</v>
       </c>
       <c r="K140">
-        <v>78.5</v>
+        <v>78.52672599978166</v>
       </c>
       <c r="L140">
         <v>654.8847712304271</v>
@@ -4924,15 +5796,27 @@
         <v>971.9620528078709</v>
       </c>
       <c r="N140">
+        <v>1626.846824038298</v>
+      </c>
+      <c r="O140">
+        <v>0.673776069074457</v>
+      </c>
+      <c r="P140">
+        <v>0.4025485138206289</v>
+      </c>
+      <c r="Q140">
+        <v>0.597451486179371</v>
+      </c>
+      <c r="R140">
         <v>145.6178214888493</v>
       </c>
-      <c r="O140">
+      <c r="S140">
         <v>276.6148773102805</v>
       </c>
-      <c r="P140">
+      <c r="T140">
         <v>1394.194751607001</v>
       </c>
-      <c r="Q140">
+      <c r="U140">
         <v>2049.079522837428</v>
       </c>
     </row>
@@ -4970,7 +5854,7 @@
         <v>0.4</v>
       </c>
       <c r="K141">
-        <v>84</v>
+        <v>83.96086926701844</v>
       </c>
       <c r="L141">
         <v>120.1416243479819</v>
@@ -4979,15 +5863,27 @@
         <v>291.6469385768867</v>
       </c>
       <c r="N141">
+        <v>411.7885629248685</v>
+      </c>
+      <c r="O141">
+        <v>0.4119420040348171</v>
+      </c>
+      <c r="P141">
+        <v>0.2917556123818376</v>
+      </c>
+      <c r="Q141">
+        <v>0.7082443876181624</v>
+      </c>
+      <c r="R141">
         <v>23.48999719429312</v>
       </c>
-      <c r="O141">
+      <c r="S141">
         <v>87.53875270028259</v>
       </c>
-      <c r="P141">
+      <c r="T141">
         <v>402.6756884714624</v>
       </c>
-      <c r="Q141">
+      <c r="U141">
         <v>522.8173128194442</v>
       </c>
     </row>
@@ -5025,7 +5921,7 @@
         <v>0.5</v>
       </c>
       <c r="K142">
-        <v>83</v>
+        <v>82.98152761888394</v>
       </c>
       <c r="L142">
         <v>274.2263688501849</v>
@@ -5034,15 +5930,27 @@
         <v>871.3648149407636</v>
       </c>
       <c r="N142">
+        <v>1145.591183790948</v>
+      </c>
+      <c r="O142">
+        <v>0.3147090221548906</v>
+      </c>
+      <c r="P142">
+        <v>0.2393754183256937</v>
+      </c>
+      <c r="Q142">
+        <v>0.7606245816743064</v>
+      </c>
+      <c r="R142">
         <v>55.21464002626827</v>
       </c>
-      <c r="O142">
+      <c r="S142">
         <v>192.8892208397024</v>
       </c>
-      <c r="P142">
+      <c r="T142">
         <v>1119.468675806734</v>
       </c>
-      <c r="Q142">
+      <c r="U142">
         <v>1393.695044656919</v>
       </c>
     </row>
@@ -5100,7 +6008,7 @@
         <v>0.3</v>
       </c>
       <c r="K145">
-        <v>86.09999999999999</v>
+        <v>86.14510387281186</v>
       </c>
       <c r="L145">
         <v>157.333190435133</v>
@@ -5109,15 +6017,27 @@
         <v>204.5459428771936</v>
       </c>
       <c r="N145">
+        <v>361.8791333123266</v>
+      </c>
+      <c r="O145">
+        <v>0.7691826502253994</v>
+      </c>
+      <c r="P145">
+        <v>0.4347672356652396</v>
+      </c>
+      <c r="Q145">
+        <v>0.5652327643347603</v>
+      </c>
+      <c r="R145">
         <v>27.85506348785725</v>
       </c>
-      <c r="O145">
+      <c r="S145">
         <v>50.29453670323532</v>
       </c>
-      <c r="P145">
+      <c r="T145">
         <v>282.6955430682862</v>
       </c>
-      <c r="Q145">
+      <c r="U145">
         <v>440.0287335034192</v>
       </c>
     </row>
@@ -5161,15 +6081,27 @@
         <v>217.8832912309327</v>
       </c>
       <c r="N146">
+        <v>340.3398684508194</v>
+      </c>
+      <c r="O146">
+        <v>0.5620283066593477</v>
+      </c>
+      <c r="P146">
+        <v>0.3598067360644295</v>
+      </c>
+      <c r="Q146">
+        <v>0.6401932639355704</v>
+      </c>
+      <c r="R146">
         <v>41.80920642975785</v>
       </c>
-      <c r="O146">
+      <c r="S146">
         <v>55.61909162485655</v>
       </c>
-      <c r="P146">
+      <c r="T146">
         <v>315.3115892855471</v>
       </c>
-      <c r="Q146">
+      <c r="U146">
         <v>437.7681665054338</v>
       </c>
     </row>
@@ -5233,15 +6165,27 @@
         <v>193.6302614967024</v>
       </c>
       <c r="N149">
+        <v>349.3477096744936</v>
+      </c>
+      <c r="O149">
+        <v>0.8041999580754747</v>
+      </c>
+      <c r="P149">
+        <v>0.4457377102110723</v>
+      </c>
+      <c r="Q149">
+        <v>0.5542622897889277</v>
+      </c>
+      <c r="R149">
         <v>36.52214050818808</v>
       </c>
-      <c r="O149">
+      <c r="S149">
         <v>32.39303532506778</v>
       </c>
-      <c r="P149">
+      <c r="T149">
         <v>262.5454373299582</v>
       </c>
-      <c r="Q149">
+      <c r="U149">
         <v>418.2628855077495</v>
       </c>
     </row>
@@ -5285,15 +6229,27 @@
         <v>293.7462355010629</v>
       </c>
       <c r="N150">
+        <v>437.9051604352171</v>
+      </c>
+      <c r="O150">
+        <v>0.4907600762551136</v>
+      </c>
+      <c r="P150">
+        <v>0.3292012471167962</v>
+      </c>
+      <c r="Q150">
+        <v>0.6707987528832038</v>
+      </c>
+      <c r="R150">
         <v>39.91802493844902</v>
       </c>
-      <c r="O150">
+      <c r="S150">
         <v>67.44676786335552</v>
       </c>
-      <c r="P150">
+      <c r="T150">
         <v>401.1110283028675</v>
       </c>
-      <c r="Q150">
+      <c r="U150">
         <v>545.2699532370216</v>
       </c>
     </row>
@@ -5340,6 +6296,9 @@
       <c r="J152">
         <v>0.515244800318323</v>
       </c>
+      <c r="K152">
+        <v>86.91749562814242</v>
+      </c>
       <c r="L152">
         <v>76.23859849445017</v>
       </c>
@@ -5347,15 +6306,27 @@
         <v>239.857714949977</v>
       </c>
       <c r="N152">
+        <v>316.0963134444272</v>
+      </c>
+      <c r="O152">
+        <v>0.3178492653878152</v>
+      </c>
+      <c r="P152">
+        <v>0.2411878761371687</v>
+      </c>
+      <c r="Q152">
+        <v>0.7588121238628311</v>
+      </c>
+      <c r="R152">
         <v>4.837754621945452</v>
       </c>
-      <c r="O152">
+      <c r="S152">
         <v>29.51622239239742</v>
       </c>
-      <c r="P152">
+      <c r="T152">
         <v>274.2116919643199</v>
       </c>
-      <c r="Q152">
+      <c r="U152">
         <v>350.4502904587701</v>
       </c>
     </row>
@@ -5392,6 +6363,9 @@
       <c r="J153">
         <v>0.4132541438747627</v>
       </c>
+      <c r="K153">
+        <v>88.22759810150885</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5436,6 +6410,9 @@
       <c r="J155">
         <v>0.3664689775535147</v>
       </c>
+      <c r="K155">
+        <v>88.29175393883509</v>
+      </c>
       <c r="L155">
         <v>232.3174311521793</v>
       </c>
@@ -5443,15 +6420,27 @@
         <v>337.4344105127956</v>
       </c>
       <c r="N155">
+        <v>569.7518416649749</v>
+      </c>
+      <c r="O155">
+        <v>0.6884817431604823</v>
+      </c>
+      <c r="P155">
+        <v>0.4077519617545816</v>
+      </c>
+      <c r="Q155">
+        <v>0.5922480382454184</v>
+      </c>
+      <c r="R155">
         <v>6.38906929816584</v>
       </c>
-      <c r="O155">
+      <c r="S155">
         <v>35.12201214148985</v>
       </c>
-      <c r="P155">
+      <c r="T155">
         <v>378.9454919524513</v>
       </c>
-      <c r="Q155">
+      <c r="U155">
         <v>611.2629231046307</v>
       </c>
     </row>
@@ -5488,6 +6477,9 @@
       <c r="J156">
         <v>0.3639023378220066</v>
       </c>
+      <c r="K156">
+        <v>89.39863179525344</v>
+      </c>
       <c r="L156">
         <v>186.0514877946553</v>
       </c>
@@ -5495,15 +6487,27 @@
         <v>307.2069004274902</v>
       </c>
       <c r="N156">
+        <v>493.2583882221454</v>
+      </c>
+      <c r="O156">
+        <v>0.6056227498007287</v>
+      </c>
+      <c r="P156">
+        <v>0.3771886950878665</v>
+      </c>
+      <c r="Q156">
+        <v>0.6228113049121335</v>
+      </c>
+      <c r="R156">
         <v>4.054015191447721</v>
       </c>
-      <c r="O156">
+      <c r="S156">
         <v>55.90988250842189</v>
       </c>
-      <c r="P156">
+      <c r="T156">
         <v>367.1707981273598</v>
       </c>
-      <c r="Q156">
+      <c r="U156">
         <v>553.222285922015</v>
       </c>
     </row>
@@ -5540,6 +6544,9 @@
       <c r="J157">
         <v>0.4556419279460224</v>
       </c>
+      <c r="K157">
+        <v>86.47014024890684</v>
+      </c>
       <c r="L157">
         <v>120.2041235847587</v>
       </c>
@@ -5547,15 +6554,27 @@
         <v>190.1563019649191</v>
       </c>
       <c r="N157">
+        <v>310.3604255496778</v>
+      </c>
+      <c r="O157">
+        <v>0.6321332627037229</v>
+      </c>
+      <c r="P157">
+        <v>0.3873049322311817</v>
+      </c>
+      <c r="Q157">
+        <v>0.6126950677688182</v>
+      </c>
+      <c r="R157">
         <v>3.635150119377731</v>
       </c>
-      <c r="O157">
+      <c r="S157">
         <v>33.26402571377518</v>
       </c>
-      <c r="P157">
+      <c r="T157">
         <v>227.055477798072</v>
       </c>
-      <c r="Q157">
+      <c r="U157">
         <v>347.2596013828307</v>
       </c>
     </row>
@@ -5613,7 +6632,7 @@
         <v>0.4</v>
       </c>
       <c r="K160">
-        <v>81.5</v>
+        <v>81.47170990273207</v>
       </c>
       <c r="L160">
         <v>798.025886537851</v>
@@ -5622,15 +6641,27 @@
         <v>782.0920890133668</v>
       </c>
       <c r="N160">
+        <v>1580.117975551218</v>
+      </c>
+      <c r="O160">
+        <v>1.020373300981199</v>
+      </c>
+      <c r="P160">
+        <v>0.5050419645149995</v>
+      </c>
+      <c r="Q160">
+        <v>0.4949580354850005</v>
+      </c>
+      <c r="R160">
         <v>84.03765195258713</v>
       </c>
-      <c r="O160">
+      <c r="S160">
         <v>192.5407019666441</v>
       </c>
-      <c r="P160">
+      <c r="T160">
         <v>1058.670442932598</v>
       </c>
-      <c r="Q160">
+      <c r="U160">
         <v>1856.696329470449</v>
       </c>
     </row>
@@ -5668,7 +6699,7 @@
         <v>0.4</v>
       </c>
       <c r="K161">
-        <v>81.09999999999999</v>
+        <v>81.11129853103513</v>
       </c>
       <c r="L161">
         <v>415.7494866394509</v>
@@ -5677,15 +6708,27 @@
         <v>252.1729113656824</v>
       </c>
       <c r="N161">
+        <v>667.9223980051333</v>
+      </c>
+      <c r="O161">
+        <v>1.648668306155065</v>
+      </c>
+      <c r="P161">
+        <v>0.6224517816458308</v>
+      </c>
+      <c r="Q161">
+        <v>0.3775482183541692</v>
+      </c>
+      <c r="R161">
         <v>46.78195447556466</v>
       </c>
-      <c r="O161">
+      <c r="S161">
         <v>92.12160399171159</v>
       </c>
-      <c r="P161">
+      <c r="T161">
         <v>391.0764698329587</v>
       </c>
-      <c r="Q161">
+      <c r="U161">
         <v>806.8259564724096</v>
       </c>
     </row>
@@ -5729,15 +6772,27 @@
         <v>247.6119443855666</v>
       </c>
       <c r="N162">
+        <v>435.6182902741255</v>
+      </c>
+      <c r="O162">
+        <v>0.7592781776141083</v>
+      </c>
+      <c r="P162">
+        <v>0.4315850598703063</v>
+      </c>
+      <c r="Q162">
+        <v>0.5684149401296936</v>
+      </c>
+      <c r="R162">
         <v>67.72537533934508</v>
       </c>
-      <c r="O162">
+      <c r="S162">
         <v>71.87226496462817</v>
       </c>
-      <c r="P162">
+      <c r="T162">
         <v>387.2095846895398</v>
       </c>
-      <c r="Q162">
+      <c r="U162">
         <v>575.2159305780988</v>
       </c>
     </row>
@@ -5795,7 +6850,7 @@
         <v>0.4</v>
       </c>
       <c r="K165">
-        <v>85.2</v>
+        <v>85.1948711778804</v>
       </c>
       <c r="L165">
         <v>488.0807662615646</v>
@@ -5804,15 +6859,27 @@
         <v>302.2422294288671</v>
       </c>
       <c r="N165">
+        <v>790.3229956904318</v>
+      </c>
+      <c r="O165">
+        <v>1.614866219005425</v>
+      </c>
+      <c r="P165">
+        <v>0.6175712574770443</v>
+      </c>
+      <c r="Q165">
+        <v>0.3824287425229556</v>
+      </c>
+      <c r="R165">
         <v>22.79615763354272</v>
       </c>
-      <c r="O165">
+      <c r="S165">
         <v>48.56838867895728</v>
       </c>
-      <c r="P165">
+      <c r="T165">
         <v>373.6067757413671</v>
       </c>
-      <c r="Q165">
+      <c r="U165">
         <v>861.6875420029318</v>
       </c>
     </row>
@@ -5850,7 +6917,7 @@
         <v>0.3</v>
       </c>
       <c r="K166">
-        <v>75.3</v>
+        <v>75.29382944604993</v>
       </c>
       <c r="L166">
         <v>549.6257208454421</v>
@@ -5859,15 +6926,27 @@
         <v>768.1932590745628</v>
       </c>
       <c r="N166">
+        <v>1317.818979920005</v>
+      </c>
+      <c r="O166">
+        <v>0.7154784481024637</v>
+      </c>
+      <c r="P166">
+        <v>0.4170722452933602</v>
+      </c>
+      <c r="Q166">
+        <v>0.5829277547066397</v>
+      </c>
+      <c r="R166">
         <v>64.86756828134932</v>
       </c>
-      <c r="O166">
+      <c r="S166">
         <v>80.5473718063967</v>
       </c>
-      <c r="P166">
+      <c r="T166">
         <v>913.6081991623088</v>
       </c>
-      <c r="Q166">
+      <c r="U166">
         <v>1463.233920007751</v>
       </c>
     </row>
@@ -5905,7 +6984,7 @@
         <v>0.3</v>
       </c>
       <c r="K167">
-        <v>78.59999999999999</v>
+        <v>78.61976063487042</v>
       </c>
       <c r="L167">
         <v>1337.539241311666</v>
@@ -5914,15 +6993,27 @@
         <v>546.2964652837352</v>
       </c>
       <c r="N167">
+        <v>1883.835706595401</v>
+      </c>
+      <c r="O167">
+        <v>2.448376158935929</v>
+      </c>
+      <c r="P167">
+        <v>0.7100084347211785</v>
+      </c>
+      <c r="Q167">
+        <v>0.2899915652788215</v>
+      </c>
+      <c r="R167">
         <v>75.08517783059774</v>
       </c>
-      <c r="O167">
+      <c r="S167">
         <v>132.0184979702851</v>
       </c>
-      <c r="P167">
+      <c r="T167">
         <v>753.4001410846181</v>
       </c>
-      <c r="Q167">
+      <c r="U167">
         <v>2090.939382396284</v>
       </c>
     </row>
@@ -5970,7 +7061,7 @@
         <v>0.3</v>
       </c>
       <c r="K169">
-        <v>67.59999999999999</v>
+        <v>67.64286951308233</v>
       </c>
       <c r="L169">
         <v>115.123772236214</v>
@@ -5979,15 +7070,27 @@
         <v>60.31314111062864</v>
       </c>
       <c r="N169">
+        <v>175.4369133468427</v>
+      </c>
+      <c r="O169">
+        <v>1.908767643606053</v>
+      </c>
+      <c r="P169">
+        <v>0.6562117973918737</v>
+      </c>
+      <c r="Q169">
+        <v>0.3437882026081263</v>
+      </c>
+      <c r="R169">
         <v>51.72970965344645</v>
       </c>
-      <c r="O169">
+      <c r="S169">
         <v>33.62081057979015</v>
       </c>
-      <c r="P169">
+      <c r="T169">
         <v>145.6636613438652</v>
       </c>
-      <c r="Q169">
+      <c r="U169">
         <v>260.7874335800793</v>
       </c>
     </row>
@@ -6031,15 +7134,27 @@
         <v>234.2586264073633</v>
       </c>
       <c r="N170">
+        <v>345.0687306611251</v>
+      </c>
+      <c r="O170">
+        <v>0.473024647814117</v>
+      </c>
+      <c r="P170">
+        <v>0.3211247337348075</v>
+      </c>
+      <c r="Q170">
+        <v>0.6788752662651925</v>
+      </c>
+      <c r="R170">
         <v>11.58577574415532</v>
       </c>
-      <c r="O170">
+      <c r="S170">
         <v>33.38876704929221</v>
       </c>
-      <c r="P170">
+      <c r="T170">
         <v>279.2331692008108</v>
       </c>
-      <c r="Q170">
+      <c r="U170">
         <v>390.0432734545727</v>
       </c>
     </row>
@@ -6077,7 +7192,7 @@
         <v>0.5</v>
       </c>
       <c r="K171">
-        <v>76.3</v>
+        <v>76.25823844822632</v>
       </c>
       <c r="L171">
         <v>178.1968251618819</v>
@@ -6086,15 +7201,27 @@
         <v>326.360678185704</v>
       </c>
       <c r="N171">
+        <v>504.5575033475859</v>
+      </c>
+      <c r="O171">
+        <v>0.546011934257856</v>
+      </c>
+      <c r="P171">
+        <v>0.3531744627314034</v>
+      </c>
+      <c r="Q171">
+        <v>0.6468255372685966</v>
+      </c>
+      <c r="R171">
         <v>17.45980444595425</v>
       </c>
-      <c r="O171">
+      <c r="S171">
         <v>27.5323113882971</v>
       </c>
-      <c r="P171">
+      <c r="T171">
         <v>371.3527940199554</v>
       </c>
-      <c r="Q171">
+      <c r="U171">
         <v>549.5496191818372</v>
       </c>
     </row>
@@ -6142,7 +7269,7 @@
         <v>0.3</v>
       </c>
       <c r="K173">
-        <v>81.8</v>
+        <v>81.83137626161277</v>
       </c>
       <c r="L173">
         <v>276.6211329892492</v>
@@ -6151,15 +7278,27 @@
         <v>337.4954088176796</v>
       </c>
       <c r="N173">
+        <v>614.1165418069288</v>
+      </c>
+      <c r="O173">
+        <v>0.8196293216500741</v>
+      </c>
+      <c r="P173">
+        <v>0.4504375214765273</v>
+      </c>
+      <c r="Q173">
+        <v>0.5495624785234726</v>
+      </c>
+      <c r="R173">
         <v>20.83923253429036</v>
       </c>
-      <c r="O173">
+      <c r="S173">
         <v>32.51731269149565</v>
       </c>
-      <c r="P173">
+      <c r="T173">
         <v>390.8519540434656</v>
       </c>
-      <c r="Q173">
+      <c r="U173">
         <v>667.4730870327148</v>
       </c>
     </row>
@@ -6207,7 +7346,7 @@
         <v>0.4</v>
       </c>
       <c r="K175">
-        <v>83.2</v>
+        <v>83.22607111118901</v>
       </c>
       <c r="L175">
         <v>123.0138882659961</v>
@@ -6216,15 +7355,27 @@
         <v>143.7197122558204</v>
       </c>
       <c r="N175">
+        <v>266.7336005218165</v>
+      </c>
+      <c r="O175">
+        <v>0.8559291299375275</v>
+      </c>
+      <c r="P175">
+        <v>0.4611863223281262</v>
+      </c>
+      <c r="Q175">
+        <v>0.5388136776718737</v>
+      </c>
+      <c r="R175">
         <v>8.903277076409493</v>
       </c>
-      <c r="O175">
+      <c r="S175">
         <v>33.70127081031469</v>
       </c>
-      <c r="P175">
+      <c r="T175">
         <v>186.3242601425445</v>
       </c>
-      <c r="Q175">
+      <c r="U175">
         <v>309.3381484085406</v>
       </c>
     </row>
@@ -6282,7 +7433,7 @@
         <v>0.4</v>
       </c>
       <c r="K178">
-        <v>75.59999999999999</v>
+        <v>75.57460614682404</v>
       </c>
       <c r="L178">
         <v>377.9627949475497</v>
@@ -6291,15 +7442,27 @@
         <v>499.9388892684253</v>
       </c>
       <c r="N178">
+        <v>877.901684215975</v>
+      </c>
+      <c r="O178">
+        <v>0.7560179915201902</v>
+      </c>
+      <c r="P178">
+        <v>0.4305297526397797</v>
+      </c>
+      <c r="Q178">
+        <v>0.5694702473602203</v>
+      </c>
+      <c r="R178">
         <v>19.38770697198028</v>
       </c>
-      <c r="O178">
+      <c r="S178">
         <v>37.88708029109406</v>
       </c>
-      <c r="P178">
+      <c r="T178">
         <v>557.2136765314997</v>
       </c>
-      <c r="Q178">
+      <c r="U178">
         <v>935.1764714790494</v>
       </c>
     </row>
@@ -6357,7 +7520,7 @@
         <v>0.3</v>
       </c>
       <c r="K181">
-        <v>78.09999999999999</v>
+        <v>78.11174067321043</v>
       </c>
       <c r="L181">
         <v>493.3909751036258</v>
@@ -6366,15 +7529,27 @@
         <v>656.8763557118664</v>
       </c>
       <c r="N181">
+        <v>1150.267330815492</v>
+      </c>
+      <c r="O181">
+        <v>0.751116965641016</v>
+      </c>
+      <c r="P181">
+        <v>0.428935919403911</v>
+      </c>
+      <c r="Q181">
+        <v>0.5710640805960889</v>
+      </c>
+      <c r="R181">
         <v>27.73855896873279</v>
       </c>
-      <c r="O181">
+      <c r="S181">
         <v>87.2699004265484</v>
       </c>
-      <c r="P181">
+      <c r="T181">
         <v>771.8848151071476</v>
       </c>
-      <c r="Q181">
+      <c r="U181">
         <v>1265.275790210773</v>
       </c>
     </row>
@@ -6422,7 +7597,7 @@
         <v>0.4</v>
       </c>
       <c r="K183">
-        <v>82</v>
+        <v>81.95108027644217</v>
       </c>
       <c r="L183">
         <v>369.3141730317938</v>
@@ -6431,15 +7606,27 @@
         <v>221.5146184206696</v>
       </c>
       <c r="N183">
+        <v>590.8287914524634</v>
+      </c>
+      <c r="O183">
+        <v>1.667222577294848</v>
+      </c>
+      <c r="P183">
+        <v>0.6250781586386314</v>
+      </c>
+      <c r="Q183">
+        <v>0.3749218413613686</v>
+      </c>
+      <c r="R183">
         <v>14.56827683817697</v>
       </c>
-      <c r="O183">
+      <c r="S183">
         <v>52.36903152218802</v>
       </c>
-      <c r="P183">
+      <c r="T183">
         <v>288.4519267810346</v>
       </c>
-      <c r="Q183">
+      <c r="U183">
         <v>657.7660998128284</v>
       </c>
     </row>
@@ -6477,7 +7664,7 @@
         <v>0.5</v>
       </c>
       <c r="K184">
-        <v>80.7</v>
+        <v>80.69870016203697</v>
       </c>
       <c r="L184">
         <v>589.632865981183</v>
@@ -6486,15 +7673,27 @@
         <v>889.415830995717</v>
       </c>
       <c r="N184">
+        <v>1479.0486969769</v>
+      </c>
+      <c r="O184">
+        <v>0.6629439744973714</v>
+      </c>
+      <c r="P184">
+        <v>0.3986568306955427</v>
+      </c>
+      <c r="Q184">
+        <v>0.6013431693044574</v>
+      </c>
+      <c r="R184">
         <v>44.89016121006509</v>
       </c>
-      <c r="O184">
+      <c r="S184">
         <v>58.4753689749382</v>
       </c>
-      <c r="P184">
+      <c r="T184">
         <v>992.7813611807203</v>
       </c>
-      <c r="Q184">
+      <c r="U184">
         <v>1582.414227161903</v>
       </c>
     </row>
@@ -6531,6 +7730,9 @@
       <c r="J185">
         <v>0.3992994473428294</v>
       </c>
+      <c r="K185">
+        <v>86.42248511101729</v>
+      </c>
       <c r="L185">
         <v>1045.149380006229</v>
       </c>
@@ -6538,15 +7740,27 @@
         <v>524.8560170804137</v>
       </c>
       <c r="N185">
+        <v>1570.005397086642</v>
+      </c>
+      <c r="O185">
+        <v>1.991306846056602</v>
+      </c>
+      <c r="P185">
+        <v>0.6656979536157296</v>
+      </c>
+      <c r="Q185">
+        <v>0.3343020463842705</v>
+      </c>
+      <c r="R185">
         <v>5.31873411084119</v>
       </c>
-      <c r="O185">
+      <c r="S185">
         <v>98.17254624744723</v>
       </c>
-      <c r="P185">
+      <c r="T185">
         <v>628.3472974387022</v>
       </c>
-      <c r="Q185">
+      <c r="U185">
         <v>1673.496677444931</v>
       </c>
     </row>
@@ -6594,7 +7808,7 @@
         <v>0.4</v>
       </c>
       <c r="K187">
-        <v>73.3</v>
+        <v>73.32145624677062</v>
       </c>
       <c r="L187">
         <v>888.0167900867636</v>
@@ -6603,15 +7817,27 @@
         <v>843.252079555517</v>
       </c>
       <c r="N187">
+        <v>1731.268869642281</v>
+      </c>
+      <c r="O187">
+        <v>1.053085799153727</v>
+      </c>
+      <c r="P187">
+        <v>0.512928295343431</v>
+      </c>
+      <c r="Q187">
+        <v>0.487071704656569</v>
+      </c>
+      <c r="R187">
         <v>50.17781974931854</v>
       </c>
-      <c r="O187">
+      <c r="S187">
         <v>167.8509611606178</v>
       </c>
-      <c r="P187">
+      <c r="T187">
         <v>1061.280860465453</v>
       </c>
-      <c r="Q187">
+      <c r="U187">
         <v>1949.297650552217</v>
       </c>
     </row>
@@ -6649,7 +7875,7 @@
         <v>0.3</v>
       </c>
       <c r="K188">
-        <v>83.7</v>
+        <v>83.66557113034662</v>
       </c>
       <c r="L188">
         <v>753.8497270882019</v>
@@ -6658,15 +7884,27 @@
         <v>562.3245850782171</v>
       </c>
       <c r="N188">
+        <v>1316.174312166419</v>
+      </c>
+      <c r="O188">
+        <v>1.340595355586924</v>
+      </c>
+      <c r="P188">
+        <v>0.5727582738242076</v>
+      </c>
+      <c r="Q188">
+        <v>0.4272417261757924</v>
+      </c>
+      <c r="R188">
         <v>37.73483619132263</v>
       </c>
-      <c r="O188">
+      <c r="S188">
         <v>60.00940419967226</v>
       </c>
-      <c r="P188">
+      <c r="T188">
         <v>660.068825469212</v>
       </c>
-      <c r="Q188">
+      <c r="U188">
         <v>1413.918552557414</v>
       </c>
     </row>
@@ -6703,6 +7941,9 @@
       <c r="J189">
         <v>0.308129314847505</v>
       </c>
+      <c r="K189">
+        <v>84.75970403039842</v>
+      </c>
       <c r="L189">
         <v>977.8834483112413</v>
       </c>
@@ -6710,15 +7951,27 @@
         <v>917.768932809333</v>
       </c>
       <c r="N189">
+        <v>1895.652381120574</v>
+      </c>
+      <c r="O189">
+        <v>1.065500708678267</v>
+      </c>
+      <c r="P189">
+        <v>0.5158558911171185</v>
+      </c>
+      <c r="Q189">
+        <v>0.4841441088828816</v>
+      </c>
+      <c r="R189">
         <v>3.967565414844302</v>
       </c>
-      <c r="O189">
+      <c r="S189">
         <v>95.05973058746187</v>
       </c>
-      <c r="P189">
+      <c r="T189">
         <v>1016.796228811639</v>
       </c>
-      <c r="Q189">
+      <c r="U189">
         <v>1994.679677122881</v>
       </c>
     </row>
@@ -6756,7 +8009,7 @@
         <v>0.3</v>
       </c>
       <c r="K190">
-        <v>74.3</v>
+        <v>74.33326230723179</v>
       </c>
       <c r="L190">
         <v>496.691213402001</v>
@@ -6765,15 +8018,27 @@
         <v>619.6351715130643</v>
       </c>
       <c r="N190">
+        <v>1116.326384915065</v>
+      </c>
+      <c r="O190">
+        <v>0.8015865403333208</v>
+      </c>
+      <c r="P190">
+        <v>0.4449336861636495</v>
+      </c>
+      <c r="Q190">
+        <v>0.5550663138363505</v>
+      </c>
+      <c r="R190">
         <v>30.41203052032781</v>
       </c>
-      <c r="O190">
+      <c r="S190">
         <v>49.55952703660884</v>
       </c>
-      <c r="P190">
+      <c r="T190">
         <v>699.6067290700009</v>
       </c>
-      <c r="Q190">
+      <c r="U190">
         <v>1196.297942472002</v>
       </c>
     </row>
@@ -6820,6 +8085,9 @@
       <c r="J192">
         <v>0.4758202009200584</v>
       </c>
+      <c r="K192">
+        <v>84.44923690761146</v>
+      </c>
       <c r="L192">
         <v>1069.109111338934</v>
       </c>
@@ -6827,15 +8095,27 @@
         <v>892.7097412229364</v>
       </c>
       <c r="N192">
+        <v>1961.818852561871</v>
+      </c>
+      <c r="O192">
+        <v>1.197599916266564</v>
+      </c>
+      <c r="P192">
+        <v>0.5449581188104203</v>
+      </c>
+      <c r="Q192">
+        <v>0.4550418811895797</v>
+      </c>
+      <c r="R192">
         <v>2.781958975799636</v>
       </c>
-      <c r="O192">
+      <c r="S192">
         <v>142.7492985366158</v>
       </c>
-      <c r="P192">
+      <c r="T192">
         <v>1038.240998735352</v>
       </c>
-      <c r="Q192">
+      <c r="U192">
         <v>2107.350110074286</v>
       </c>
     </row>
@@ -6873,7 +8153,7 @@
         <v>0.4</v>
       </c>
       <c r="K193">
-        <v>80</v>
+        <v>80.02281491167277</v>
       </c>
       <c r="L193">
         <v>171.5519152218291</v>
@@ -6882,15 +8162,27 @@
         <v>329.8507926748941</v>
       </c>
       <c r="N193">
+        <v>501.4027078967232</v>
+      </c>
+      <c r="O193">
+        <v>0.5200894435652098</v>
+      </c>
+      <c r="P193">
+        <v>0.3421439743344278</v>
+      </c>
+      <c r="Q193">
+        <v>0.6578560256655722</v>
+      </c>
+      <c r="R193">
         <v>15.25333608837281</v>
       </c>
-      <c r="O193">
+      <c r="S193">
         <v>22.71327824392704</v>
       </c>
-      <c r="P193">
+      <c r="T193">
         <v>367.817407007194</v>
       </c>
-      <c r="Q193">
+      <c r="U193">
         <v>539.3693222290231</v>
       </c>
     </row>
@@ -6928,7 +8220,7 @@
         <v>0.2</v>
       </c>
       <c r="K194">
-        <v>82.90000000000001</v>
+        <v>82.93895431076322</v>
       </c>
       <c r="L194">
         <v>371.7960206892124</v>
@@ -6937,15 +8229,27 @@
         <v>365.0196544418155</v>
       </c>
       <c r="N194">
+        <v>736.8156751310279</v>
+      </c>
+      <c r="O194">
+        <v>1.018564387328017</v>
+      </c>
+      <c r="P194">
+        <v>0.5045984134676503</v>
+      </c>
+      <c r="Q194">
+        <v>0.4954015865323496</v>
+      </c>
+      <c r="R194">
         <v>20.05316597896929</v>
       </c>
-      <c r="O194">
+      <c r="S194">
         <v>29.47880531984422</v>
       </c>
-      <c r="P194">
+      <c r="T194">
         <v>414.551625740629</v>
       </c>
-      <c r="Q194">
+      <c r="U194">
         <v>786.3476464298415</v>
       </c>
     </row>
@@ -6982,6 +8286,9 @@
       <c r="J195">
         <v>0.2777326707112347</v>
       </c>
+      <c r="K195">
+        <v>78.21000566144136</v>
+      </c>
       <c r="L195">
         <v>945.0607788206942</v>
       </c>
@@ -6989,15 +8296,27 @@
         <v>846.6776107675773</v>
       </c>
       <c r="N195">
+        <v>1791.738389588272</v>
+      </c>
+      <c r="O195">
+        <v>1.116199090187262</v>
+      </c>
+      <c r="P195">
+        <v>0.527454668780001</v>
+      </c>
+      <c r="Q195">
+        <v>0.472545331219999</v>
+      </c>
+      <c r="R195">
         <v>6.09446627437876</v>
       </c>
-      <c r="O195">
+      <c r="S195">
         <v>181.3550195586278</v>
       </c>
-      <c r="P195">
+      <c r="T195">
         <v>1034.127096600584</v>
       </c>
-      <c r="Q195">
+      <c r="U195">
         <v>1979.187875421278</v>
       </c>
     </row>
@@ -7041,15 +8360,27 @@
         <v>86.29873613802769</v>
       </c>
       <c r="N196">
+        <v>222.772586455509</v>
+      </c>
+      <c r="O196">
+        <v>1.581411923567487</v>
+      </c>
+      <c r="P196">
+        <v>0.6126150999496394</v>
+      </c>
+      <c r="Q196">
+        <v>0.3873849000503606</v>
+      </c>
+      <c r="R196">
         <v>46.03861298099812</v>
       </c>
-      <c r="O196">
+      <c r="S196">
         <v>32.74383063056445</v>
       </c>
-      <c r="P196">
+      <c r="T196">
         <v>165.0811797495903</v>
       </c>
-      <c r="Q196">
+      <c r="U196">
         <v>301.5550300670716</v>
       </c>
     </row>
@@ -7087,7 +8418,7 @@
         <v>0.5</v>
       </c>
       <c r="K197">
-        <v>78.5</v>
+        <v>78.48632767643267</v>
       </c>
     </row>
     <row r="198">
@@ -7130,15 +8461,27 @@
         <v>911.1908784174022</v>
       </c>
       <c r="N198">
+        <v>1272.664732625321</v>
+      </c>
+      <c r="O198">
+        <v>0.3967048647762393</v>
+      </c>
+      <c r="P198">
+        <v>0.2840291279717093</v>
+      </c>
+      <c r="Q198">
+        <v>0.7159708720282908</v>
+      </c>
+      <c r="R198">
         <v>76.67978290172664</v>
       </c>
-      <c r="O198">
+      <c r="S198">
         <v>271.5167219327728</v>
       </c>
-      <c r="P198">
+      <c r="T198">
         <v>1259.387383251902</v>
       </c>
-      <c r="Q198">
+      <c r="U198">
         <v>1620.86123745982</v>
       </c>
     </row>
@@ -7186,7 +8529,7 @@
         <v>0.6</v>
       </c>
       <c r="K200">
-        <v>81.40000000000001</v>
+        <v>81.37722269222269</v>
       </c>
       <c r="L200">
         <v>96.59045899174615</v>
@@ -7195,15 +8538,27 @@
         <v>260.1531627489938</v>
       </c>
       <c r="N200">
+        <v>356.74362174074</v>
+      </c>
+      <c r="O200">
+        <v>0.3712830471522673</v>
+      </c>
+      <c r="P200">
+        <v>0.270755952188943</v>
+      </c>
+      <c r="Q200">
+        <v>0.729244047811057</v>
+      </c>
+      <c r="R200">
         <v>15.75281734018687</v>
       </c>
-      <c r="O200">
+      <c r="S200">
         <v>33.14892105846091</v>
       </c>
-      <c r="P200">
+      <c r="T200">
         <v>309.0549011476416</v>
       </c>
-      <c r="Q200">
+      <c r="U200">
         <v>405.6453601393878</v>
       </c>
     </row>
@@ -7261,7 +8616,7 @@
         <v>0.4</v>
       </c>
       <c r="K203">
-        <v>80.5</v>
+        <v>80.49530548236598</v>
       </c>
       <c r="L203">
         <v>376.0357516973307</v>
@@ -7270,15 +8625,27 @@
         <v>266.1452403325625</v>
       </c>
       <c r="N203">
+        <v>642.1809920298932</v>
+      </c>
+      <c r="O203">
+        <v>1.412896774811581</v>
+      </c>
+      <c r="P203">
+        <v>0.5855603893050549</v>
+      </c>
+      <c r="Q203">
+        <v>0.414439610694945</v>
+      </c>
+      <c r="R203">
         <v>56.10403184326301</v>
       </c>
-      <c r="O203">
+      <c r="S203">
         <v>69.70089520446028</v>
       </c>
-      <c r="P203">
+      <c r="T203">
         <v>391.9501673802858</v>
       </c>
-      <c r="Q203">
+      <c r="U203">
         <v>767.9859190776165</v>
       </c>
     </row>
@@ -7326,7 +8693,7 @@
         <v>0.3</v>
       </c>
       <c r="K205">
-        <v>74</v>
+        <v>74.04343193846026</v>
       </c>
       <c r="L205">
         <v>226.709116235846</v>
@@ -7335,15 +8702,27 @@
         <v>418.6425154894059</v>
       </c>
       <c r="N205">
+        <v>645.3516317252519</v>
+      </c>
+      <c r="O205">
+        <v>0.5415339050569579</v>
+      </c>
+      <c r="P205">
+        <v>0.3512954877479317</v>
+      </c>
+      <c r="Q205">
+        <v>0.6487045122520683</v>
+      </c>
+      <c r="R205">
         <v>25.72257689530233</v>
       </c>
-      <c r="O205">
+      <c r="S205">
         <v>43.0916689794485</v>
       </c>
-      <c r="P205">
+      <c r="T205">
         <v>487.4567613641568</v>
       </c>
-      <c r="Q205">
+      <c r="U205">
         <v>714.1658776000028</v>
       </c>
     </row>
@@ -7380,6 +8759,9 @@
       <c r="J206">
         <v>0.4073925182103832</v>
       </c>
+      <c r="K206">
+        <v>85.28973172243829</v>
+      </c>
       <c r="L206">
         <v>284.4903104104421</v>
       </c>
@@ -7387,15 +8769,27 @@
         <v>330.3919280749648</v>
       </c>
       <c r="N206">
+        <v>614.8822384854069</v>
+      </c>
+      <c r="O206">
+        <v>0.8610691915750808</v>
+      </c>
+      <c r="P206">
+        <v>0.4626744644815334</v>
+      </c>
+      <c r="Q206">
+        <v>0.5373255355184666</v>
+      </c>
+      <c r="R206">
         <v>7.256089483317819</v>
       </c>
-      <c r="O206">
+      <c r="S206">
         <v>51.75885171715745</v>
       </c>
-      <c r="P206">
+      <c r="T206">
         <v>389.40686927544</v>
       </c>
-      <c r="Q206">
+      <c r="U206">
         <v>673.8971796858822</v>
       </c>
     </row>
@@ -7432,6 +8826,9 @@
       <c r="J207">
         <v>0.3635177189459834</v>
       </c>
+      <c r="K207">
+        <v>87.29759285177758</v>
+      </c>
       <c r="L207">
         <v>508.4771983609588</v>
       </c>
@@ -7439,15 +8836,27 @@
         <v>192.3124589380043</v>
       </c>
       <c r="N207">
+        <v>700.7896572989631</v>
+      </c>
+      <c r="O207">
+        <v>2.644015895636156</v>
+      </c>
+      <c r="P207">
+        <v>0.7255774868607086</v>
+      </c>
+      <c r="Q207">
+        <v>0.2744225131392915</v>
+      </c>
+      <c r="R207">
         <v>1.284072914417196</v>
       </c>
-      <c r="O207">
+      <c r="S207">
         <v>36.66460613680475</v>
       </c>
-      <c r="P207">
+      <c r="T207">
         <v>230.2611379892263</v>
       </c>
-      <c r="Q207">
+      <c r="U207">
         <v>738.738336350185</v>
       </c>
     </row>
@@ -7491,15 +8900,27 @@
         <v>280.6168909977894</v>
       </c>
       <c r="N208">
+        <v>699.4899044700487</v>
+      </c>
+      <c r="O208">
+        <v>1.492686388131779</v>
+      </c>
+      <c r="P208">
+        <v>0.5988263887662656</v>
+      </c>
+      <c r="Q208">
+        <v>0.4011736112337345</v>
+      </c>
+      <c r="R208">
         <v>21.3135481856189</v>
       </c>
-      <c r="O208">
+      <c r="S208">
         <v>66.13910800777222</v>
       </c>
-      <c r="P208">
+      <c r="T208">
         <v>368.0695471911805</v>
       </c>
-      <c r="Q208">
+      <c r="U208">
         <v>786.9425606634397</v>
       </c>
     </row>
@@ -7536,6 +8957,9 @@
       <c r="J209">
         <v>0.3214308220021428</v>
       </c>
+      <c r="K209">
+        <v>89.78684845067102</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7570,6 +8994,9 @@
       <c r="J210">
         <v>0.3621217018975001</v>
       </c>
+      <c r="K210">
+        <v>81.25374470163052</v>
+      </c>
       <c r="L210">
         <v>223.3290754563795</v>
       </c>
@@ -7577,15 +9004,27 @@
         <v>456.4180240158873</v>
       </c>
       <c r="N210">
+        <v>679.7470994722669</v>
+      </c>
+      <c r="O210">
+        <v>0.4893081861478059</v>
+      </c>
+      <c r="P210">
+        <v>0.3285473018270543</v>
+      </c>
+      <c r="Q210">
+        <v>0.6714526981729457</v>
+      </c>
+      <c r="R210">
         <v>6.261789007294015</v>
       </c>
-      <c r="O210">
+      <c r="S210">
         <v>33.14989139077778</v>
       </c>
-      <c r="P210">
+      <c r="T210">
         <v>495.8297044139591</v>
       </c>
-      <c r="Q210">
+      <c r="U210">
         <v>719.1587798703388</v>
       </c>
     </row>
@@ -7622,6 +9061,9 @@
       <c r="J211">
         <v>0.340019022392692</v>
       </c>
+      <c r="K211">
+        <v>83.73292916486795</v>
+      </c>
       <c r="L211">
         <v>229.3132374441641</v>
       </c>
@@ -7629,15 +9071,27 @@
         <v>377.4635124315441</v>
       </c>
       <c r="N211">
+        <v>606.7767498757082</v>
+      </c>
+      <c r="O211">
+        <v>0.6075110040887775</v>
+      </c>
+      <c r="P211">
+        <v>0.3779202770889565</v>
+      </c>
+      <c r="Q211">
+        <v>0.6220797229110435</v>
+      </c>
+      <c r="R211">
         <v>19.00177388450378</v>
       </c>
-      <c r="O211">
+      <c r="S211">
         <v>30.95494974185976</v>
       </c>
-      <c r="P211">
+      <c r="T211">
         <v>427.4202360579077</v>
       </c>
-      <c r="Q211">
+      <c r="U211">
         <v>656.7334735020718</v>
       </c>
     </row>
@@ -7675,7 +9129,7 @@
         <v>0.1</v>
       </c>
       <c r="K212">
-        <v>80.3</v>
+        <v>80.29763285094492</v>
       </c>
     </row>
     <row r="213">
@@ -7712,7 +9166,7 @@
         <v>0.4</v>
       </c>
       <c r="K213">
-        <v>84.09999999999999</v>
+        <v>84.14778005396536</v>
       </c>
       <c r="L213">
         <v>119.8248598034436</v>
@@ -7721,15 +9175,27 @@
         <v>140.2389058863927</v>
       </c>
       <c r="N213">
+        <v>260.0637656898363</v>
+      </c>
+      <c r="O213">
+        <v>0.85443378958271</v>
+      </c>
+      <c r="P213">
+        <v>0.4607518447854519</v>
+      </c>
+      <c r="Q213">
+        <v>0.5392481552145483</v>
+      </c>
+      <c r="R213">
         <v>22.75495691593433</v>
       </c>
-      <c r="O213">
+      <c r="S213">
         <v>49.16278523982248</v>
       </c>
-      <c r="P213">
+      <c r="T213">
         <v>212.1566480421495</v>
       </c>
-      <c r="Q213">
+      <c r="U213">
         <v>331.9815078455931</v>
       </c>
     </row>
@@ -7767,7 +9233,7 @@
         <v>0.3</v>
       </c>
       <c r="K214">
-        <v>74.3</v>
+        <v>74.28125710240312</v>
       </c>
       <c r="L214">
         <v>301.8078576186025</v>
@@ -7776,15 +9242,27 @@
         <v>490.110713498639</v>
       </c>
       <c r="N214">
+        <v>791.9185711172415</v>
+      </c>
+      <c r="O214">
+        <v>0.6157952668778798</v>
+      </c>
+      <c r="P214">
+        <v>0.3811097108037395</v>
+      </c>
+      <c r="Q214">
+        <v>0.6188902891962605</v>
+      </c>
+      <c r="R214">
         <v>40.48555257933047</v>
       </c>
-      <c r="O214">
+      <c r="S214">
         <v>36.88378500024766</v>
       </c>
-      <c r="P214">
+      <c r="T214">
         <v>567.4800510782172</v>
       </c>
-      <c r="Q214">
+      <c r="U214">
         <v>869.2879086968197</v>
       </c>
     </row>
@@ -7821,6 +9299,9 @@
       <c r="J215">
         <v>0.3632503802530237</v>
       </c>
+      <c r="K215">
+        <v>85.74587611732656</v>
+      </c>
       <c r="L215">
         <v>241.81069562156</v>
       </c>
@@ -7828,15 +9309,27 @@
         <v>257.3225675868493</v>
       </c>
       <c r="N215">
+        <v>499.1332632084093</v>
+      </c>
+      <c r="O215">
+        <v>0.9397181828599083</v>
+      </c>
+      <c r="P215">
+        <v>0.4844611919213923</v>
+      </c>
+      <c r="Q215">
+        <v>0.5155388080786077</v>
+      </c>
+      <c r="R215">
         <v>3.823445941703088</v>
       </c>
-      <c r="O215">
+      <c r="S215">
         <v>30.62731136002165</v>
       </c>
-      <c r="P215">
+      <c r="T215">
         <v>291.7733248885741</v>
       </c>
-      <c r="Q215">
+      <c r="U215">
         <v>533.5840205101341</v>
       </c>
     </row>
@@ -7883,6 +9376,9 @@
       <c r="J217">
         <v>0.5191789148317382</v>
       </c>
+      <c r="K217">
+        <v>88.47555402085737</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7894,7 +9390,7 @@
         <v>24</v>
       </c>
       <c r="K218">
-        <v>83</v>
+        <v>83.0150746019313</v>
       </c>
       <c r="L218">
         <v>295.3021229664094</v>
@@ -7903,15 +9399,27 @@
         <v>376.4037166060981</v>
       </c>
       <c r="N218">
+        <v>671.7058395725076</v>
+      </c>
+      <c r="O218">
+        <v>0.7845356194382094</v>
+      </c>
+      <c r="P218">
+        <v>0.4396301261194155</v>
+      </c>
+      <c r="Q218">
+        <v>0.5603698738805843</v>
+      </c>
+      <c r="R218">
         <v>16.56127367655098</v>
       </c>
-      <c r="O218">
+      <c r="S218">
         <v>29.55977917813026</v>
       </c>
-      <c r="P218">
+      <c r="T218">
         <v>422.5247694607793</v>
       </c>
-      <c r="Q218">
+      <c r="U218">
         <v>717.8268924271888</v>
       </c>
     </row>
@@ -7959,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="K220">
-        <v>84.40000000000001</v>
+        <v>84.38346825580413</v>
       </c>
       <c r="L220">
         <v>164.7299760702151</v>
@@ -7968,15 +9476,27 @@
         <v>256.4448186835685</v>
       </c>
       <c r="N220">
+        <v>421.1747947537836</v>
+      </c>
+      <c r="O220">
+        <v>0.6423603210852085</v>
+      </c>
+      <c r="P220">
+        <v>0.3911202145097865</v>
+      </c>
+      <c r="Q220">
+        <v>0.6088797854902136</v>
+      </c>
+      <c r="R220">
         <v>12.86906210218044</v>
       </c>
-      <c r="O220">
+      <c r="S220">
         <v>23.68024879229097</v>
       </c>
-      <c r="P220">
+      <c r="T220">
         <v>292.9941295780399</v>
       </c>
-      <c r="Q220">
+      <c r="U220">
         <v>457.724105648255</v>
       </c>
     </row>
@@ -8023,6 +9543,9 @@
       <c r="J222">
         <v>0.3455744223789519</v>
       </c>
+      <c r="K222">
+        <v>88.56671558001352</v>
+      </c>
       <c r="L222">
         <v>256.508931677618</v>
       </c>
@@ -8030,15 +9553,27 @@
         <v>218.3777033432634</v>
       </c>
       <c r="N222">
+        <v>474.8866350208813</v>
+      </c>
+      <c r="O222">
+        <v>1.174611362563956</v>
+      </c>
+      <c r="P222">
+        <v>0.5401477168679194</v>
+      </c>
+      <c r="Q222">
+        <v>0.4598522831320807</v>
+      </c>
+      <c r="R222">
         <v>3.747120655959677</v>
       </c>
-      <c r="O222">
+      <c r="S222">
         <v>20.38946826934329</v>
       </c>
-      <c r="P222">
+      <c r="T222">
         <v>242.5142922685664</v>
       </c>
-      <c r="Q222">
+      <c r="U222">
         <v>499.0232239461843</v>
       </c>
     </row>
@@ -8106,7 +9641,7 @@
         <v>0.4</v>
       </c>
       <c r="K226">
-        <v>81.3</v>
+        <v>81.3084969587002</v>
       </c>
       <c r="L226">
         <v>304.3039587389432</v>
@@ -8115,15 +9650,27 @@
         <v>427.6343277828989</v>
       </c>
       <c r="N226">
+        <v>731.9382865218422</v>
+      </c>
+      <c r="O226">
+        <v>0.7115985293244091</v>
+      </c>
+      <c r="P226">
+        <v>0.4157508417615237</v>
+      </c>
+      <c r="Q226">
+        <v>0.5842491582384762</v>
+      </c>
+      <c r="R226">
         <v>26.06130803789627</v>
       </c>
-      <c r="O226">
+      <c r="S226">
         <v>60.21791021928871</v>
       </c>
-      <c r="P226">
+      <c r="T226">
         <v>513.9135460400839</v>
       </c>
-      <c r="Q226">
+      <c r="U226">
         <v>818.2175047790272</v>
       </c>
     </row>
@@ -8160,6 +9707,9 @@
       <c r="J227">
         <v>0.3324786299518377</v>
       </c>
+      <c r="K227">
+        <v>79.982425323991</v>
+      </c>
       <c r="L227">
         <v>321.9488693301651</v>
       </c>
@@ -8167,15 +9717,27 @@
         <v>767.5083980490233</v>
       </c>
       <c r="N227">
+        <v>1089.457267379188</v>
+      </c>
+      <c r="O227">
+        <v>0.4194727642701326</v>
+      </c>
+      <c r="P227">
+        <v>0.2955130769880026</v>
+      </c>
+      <c r="Q227">
+        <v>0.7044869230119973</v>
+      </c>
+      <c r="R227">
         <v>5.440780796908602</v>
       </c>
-      <c r="O227">
+      <c r="S227">
         <v>54.08131100965207</v>
       </c>
-      <c r="P227">
+      <c r="T227">
         <v>827.0304898555839</v>
       </c>
-      <c r="Q227">
+      <c r="U227">
         <v>1148.979359185749</v>
       </c>
     </row>
@@ -8222,6 +9784,9 @@
       <c r="J229">
         <v>0.4670602913110397</v>
       </c>
+      <c r="K229">
+        <v>78.20361806470802</v>
+      </c>
       <c r="L229">
         <v>285.5981373650394</v>
       </c>
@@ -8229,15 +9794,27 @@
         <v>544.3540776346646</v>
       </c>
       <c r="N229">
+        <v>829.952214999704</v>
+      </c>
+      <c r="O229">
+        <v>0.5246550895807094</v>
+      </c>
+      <c r="P229">
+        <v>0.3441139528317799</v>
+      </c>
+      <c r="Q229">
+        <v>0.6558860471682201</v>
+      </c>
+      <c r="R229">
         <v>4.650463525845954</v>
       </c>
-      <c r="O229">
+      <c r="S229">
         <v>56.50488664553251</v>
       </c>
-      <c r="P229">
+      <c r="T229">
         <v>605.509427806043</v>
       </c>
-      <c r="Q229">
+      <c r="U229">
         <v>891.1075651710823</v>
       </c>
     </row>
@@ -8275,7 +9852,7 @@
         <v>0.3</v>
       </c>
       <c r="K230">
-        <v>85</v>
+        <v>85.00435927112204</v>
       </c>
       <c r="L230">
         <v>293.3485576494068</v>
@@ -8284,15 +9861,27 @@
         <v>257.8940888878683</v>
       </c>
       <c r="N230">
+        <v>551.242646537275</v>
+      </c>
+      <c r="O230">
+        <v>1.137476856931583</v>
+      </c>
+      <c r="P230">
+        <v>0.5321586772941569</v>
+      </c>
+      <c r="Q230">
+        <v>0.4678413227058431</v>
+      </c>
+      <c r="R230">
         <v>26.87646185242698</v>
       </c>
-      <c r="O230">
+      <c r="S230">
         <v>42.94842818318594</v>
       </c>
-      <c r="P230">
+      <c r="T230">
         <v>327.7189789234812</v>
       </c>
-      <c r="Q230">
+      <c r="U230">
         <v>621.0675365728879</v>
       </c>
     </row>
@@ -8329,6 +9918,9 @@
       <c r="J231">
         <v>0.409073694018404</v>
       </c>
+      <c r="K231">
+        <v>87.54591631214075</v>
+      </c>
       <c r="L231">
         <v>299.2969055146613</v>
       </c>
@@ -8336,15 +9928,27 @@
         <v>311.4246632351168</v>
       </c>
       <c r="N231">
+        <v>610.721568749778</v>
+      </c>
+      <c r="O231">
+        <v>0.9610571699926688</v>
+      </c>
+      <c r="P231">
+        <v>0.4900709600405284</v>
+      </c>
+      <c r="Q231">
+        <v>0.5099290399594717</v>
+      </c>
+      <c r="R231">
         <v>4.130563202498424</v>
       </c>
-      <c r="O231">
+      <c r="S231">
         <v>52.57112478435864</v>
       </c>
-      <c r="P231">
+      <c r="T231">
         <v>368.1263512219738</v>
       </c>
-      <c r="Q231">
+      <c r="U231">
         <v>667.4232567366352</v>
       </c>
     </row>
@@ -8381,6 +9985,9 @@
       <c r="J232">
         <v>0.4166426761560817</v>
       </c>
+      <c r="K232">
+        <v>86.50785260638062</v>
+      </c>
       <c r="L232">
         <v>77.36893578234852</v>
       </c>
@@ -8388,15 +9995,27 @@
         <v>132.3600596231984</v>
       </c>
       <c r="N232">
+        <v>209.7289954055469</v>
+      </c>
+      <c r="O232">
+        <v>0.5845338541143136</v>
+      </c>
+      <c r="P232">
+        <v>0.3688995679054412</v>
+      </c>
+      <c r="Q232">
+        <v>0.6311004320945589</v>
+      </c>
+      <c r="R232">
         <v>2.513631409588676</v>
       </c>
-      <c r="O232">
+      <c r="S232">
         <v>19.551441068557</v>
       </c>
-      <c r="P232">
+      <c r="T232">
         <v>154.4251321013441</v>
       </c>
-      <c r="Q232">
+      <c r="U232">
         <v>231.7940678836926</v>
       </c>
     </row>
@@ -8434,7 +10053,7 @@
         <v>0.4</v>
       </c>
       <c r="K233">
-        <v>80</v>
+        <v>80.04583959546008</v>
       </c>
       <c r="L233">
         <v>302.5601240937407</v>
@@ -8443,15 +10062,27 @@
         <v>678.8902333401954</v>
       </c>
       <c r="N233">
+        <v>981.4503574339361</v>
+      </c>
+      <c r="O233">
+        <v>0.4456686946358326</v>
+      </c>
+      <c r="P233">
+        <v>0.3082785815930652</v>
+      </c>
+      <c r="Q233">
+        <v>0.6917214184069348</v>
+      </c>
+      <c r="R233">
         <v>77.54545614861928</v>
       </c>
-      <c r="O233">
+      <c r="S233">
         <v>178.1554317560108</v>
       </c>
-      <c r="P233">
+      <c r="T233">
         <v>934.5911212448254</v>
       </c>
-      <c r="Q233">
+      <c r="U233">
         <v>1237.151245338566</v>
       </c>
     </row>
@@ -8489,7 +10120,7 @@
         <v>0.5</v>
       </c>
       <c r="K234">
-        <v>78.5</v>
+        <v>78.45333241339603</v>
       </c>
       <c r="L234">
         <v>337.7778210685444</v>
@@ -8498,15 +10129,27 @@
         <v>398.1757459016571</v>
       </c>
       <c r="N234">
+        <v>735.9535669702016</v>
+      </c>
+      <c r="O234">
+        <v>0.8483134006659713</v>
+      </c>
+      <c r="P234">
+        <v>0.4589662123102678</v>
+      </c>
+      <c r="Q234">
+        <v>0.5410337876897322</v>
+      </c>
+      <c r="R234">
         <v>69.40764427780805</v>
       </c>
-      <c r="O234">
+      <c r="S234">
         <v>119.4288661325506</v>
       </c>
-      <c r="P234">
+      <c r="T234">
         <v>587.0122563120158</v>
       </c>
-      <c r="Q234">
+      <c r="U234">
         <v>924.7900773805602</v>
       </c>
     </row>
@@ -8564,7 +10207,7 @@
         <v>0.5</v>
       </c>
       <c r="K237">
-        <v>76.2</v>
+        <v>76.1622192626285</v>
       </c>
       <c r="L237">
         <v>842.4941875865413</v>
@@ -8573,15 +10216,27 @@
         <v>1095.696547204221</v>
       </c>
       <c r="N237">
+        <v>1938.190734790762</v>
+      </c>
+      <c r="O237">
+        <v>0.7689119672196189</v>
+      </c>
+      <c r="P237">
+        <v>0.4346807424386399</v>
+      </c>
+      <c r="Q237">
+        <v>0.5653192575613601</v>
+      </c>
+      <c r="R237">
         <v>114.6564072948493</v>
       </c>
-      <c r="O237">
+      <c r="S237">
         <v>196.1815497937466</v>
       </c>
-      <c r="P237">
+      <c r="T237">
         <v>1406.534504292817</v>
       </c>
-      <c r="Q237">
+      <c r="U237">
         <v>2249.028691879358</v>
       </c>
     </row>
@@ -8639,7 +10294,7 @@
         <v>0.5</v>
       </c>
       <c r="K240">
-        <v>79.5</v>
+        <v>79.54028293428475</v>
       </c>
       <c r="L240">
         <v>325.8913679310632</v>
@@ -8648,15 +10303,27 @@
         <v>384.3771404192116</v>
       </c>
       <c r="N240">
+        <v>710.2685083502748</v>
+      </c>
+      <c r="O240">
+        <v>0.8478427400121601</v>
+      </c>
+      <c r="P240">
+        <v>0.4588284065810604</v>
+      </c>
+      <c r="Q240">
+        <v>0.5411715934189396</v>
+      </c>
+      <c r="R240">
         <v>53.38602319440444</v>
       </c>
-      <c r="O240">
+      <c r="S240">
         <v>74.62029101704991</v>
       </c>
-      <c r="P240">
+      <c r="T240">
         <v>512.3834546306659</v>
       </c>
-      <c r="Q240">
+      <c r="U240">
         <v>838.2748225617291</v>
       </c>
     </row>
@@ -8714,7 +10381,7 @@
         <v>0.4</v>
       </c>
       <c r="K243">
-        <v>81.8</v>
+        <v>81.80912896420919</v>
       </c>
       <c r="L243">
         <v>338.3145783624686</v>
@@ -8723,15 +10390,27 @@
         <v>243.8870571146821</v>
       </c>
       <c r="N243">
+        <v>582.2016354771507</v>
+      </c>
+      <c r="O243">
+        <v>1.387177254770778</v>
+      </c>
+      <c r="P243">
+        <v>0.5810952043877352</v>
+      </c>
+      <c r="Q243">
+        <v>0.4189047956122647</v>
+      </c>
+      <c r="R243">
         <v>36.61334260566903</v>
       </c>
-      <c r="O243">
+      <c r="S243">
         <v>94.66398503547836</v>
       </c>
-      <c r="P243">
+      <c r="T243">
         <v>375.1643847558295</v>
       </c>
-      <c r="Q243">
+      <c r="U243">
         <v>713.4789631182981</v>
       </c>
     </row>
@@ -8809,7 +10488,7 @@
         <v>0.4</v>
       </c>
       <c r="K248">
-        <v>83.3</v>
+        <v>83.32342581497352</v>
       </c>
       <c r="L248">
         <v>233.3142369436023</v>
@@ -8818,15 +10497,27 @@
         <v>116.3181139006046</v>
       </c>
       <c r="N248">
+        <v>349.6323508442069</v>
+      </c>
+      <c r="O248">
+        <v>2.005828921392007</v>
+      </c>
+      <c r="P248">
+        <v>0.6673130686569821</v>
+      </c>
+      <c r="Q248">
+        <v>0.3326869313430179</v>
+      </c>
+      <c r="R248">
         <v>36.32800336564149</v>
       </c>
-      <c r="O248">
+      <c r="S248">
         <v>41.52611347690112</v>
       </c>
-      <c r="P248">
+      <c r="T248">
         <v>194.1722307431472</v>
       </c>
-      <c r="Q248">
+      <c r="U248">
         <v>427.4864676867496</v>
       </c>
     </row>
@@ -8864,7 +10555,7 @@
         <v>0.4</v>
       </c>
       <c r="K249">
-        <v>83.5</v>
+        <v>83.49811238185245</v>
       </c>
     </row>
     <row r="250">
@@ -8917,15 +10608,27 @@
         <v>182.3610999091906</v>
       </c>
       <c r="N251">
+        <v>444.5555551749113</v>
+      </c>
+      <c r="O251">
+        <v>1.437776232959136</v>
+      </c>
+      <c r="P251">
+        <v>0.5897900773336637</v>
+      </c>
+      <c r="Q251">
+        <v>0.4102099226663363</v>
+      </c>
+      <c r="R251">
         <v>51.05357635029019</v>
       </c>
-      <c r="O251">
+      <c r="S251">
         <v>42.65404059700814</v>
       </c>
-      <c r="P251">
+      <c r="T251">
         <v>276.0687168564889</v>
       </c>
-      <c r="Q251">
+      <c r="U251">
         <v>538.2631721222097</v>
       </c>
     </row>
@@ -8963,7 +10666,7 @@
         <v>0.4</v>
       </c>
       <c r="K252">
-        <v>84.59999999999999</v>
+        <v>84.62385776509817</v>
       </c>
       <c r="L252">
         <v>86.30364885203846</v>
@@ -8972,15 +10675,27 @@
         <v>97.714548507854</v>
       </c>
       <c r="N252">
+        <v>184.0181973598925</v>
+      </c>
+      <c r="O252">
+        <v>0.8832221012114857</v>
+      </c>
+      <c r="P252">
+        <v>0.468995186836064</v>
+      </c>
+      <c r="Q252">
+        <v>0.531004813163936</v>
+      </c>
+      <c r="R252">
         <v>29.59664158220158</v>
       </c>
-      <c r="O252">
+      <c r="S252">
         <v>36.84495385857762</v>
       </c>
-      <c r="P252">
+      <c r="T252">
         <v>164.1561439486332</v>
       </c>
-      <c r="Q252">
+      <c r="U252">
         <v>250.4597928006717</v>
       </c>
     </row>
@@ -9038,7 +10753,7 @@
         <v>0.1</v>
       </c>
       <c r="K255">
-        <v>83.40000000000001</v>
+        <v>83.44154222896029</v>
       </c>
     </row>
     <row r="256">
@@ -9155,7 +10870,7 @@
         <v>0.6</v>
       </c>
       <c r="K264">
-        <v>79.5</v>
+        <v>79.47203674012687</v>
       </c>
       <c r="L264">
         <v>66.32120607810032</v>
@@ -9164,15 +10879,27 @@
         <v>117.8790535438179</v>
       </c>
       <c r="N264">
+        <v>184.2002596219182</v>
+      </c>
+      <c r="O264">
+        <v>0.5626207887175433</v>
+      </c>
+      <c r="P264">
+        <v>0.3600494712343429</v>
+      </c>
+      <c r="Q264">
+        <v>0.6399505287656572</v>
+      </c>
+      <c r="R264">
         <v>19.15340042213581</v>
       </c>
-      <c r="O264">
+      <c r="S264">
         <v>35.50653664358081</v>
       </c>
-      <c r="P264">
+      <c r="T264">
         <v>172.5389906095345</v>
       </c>
-      <c r="Q264">
+      <c r="U264">
         <v>238.8601966876348</v>
       </c>
     </row>
@@ -9300,7 +11027,7 @@
         <v>0.5</v>
       </c>
       <c r="K274">
-        <v>80.3</v>
+        <v>80.27442604708308</v>
       </c>
     </row>
     <row r="275">
@@ -9337,7 +11064,7 @@
         <v>0.5</v>
       </c>
       <c r="K275">
-        <v>77</v>
+        <v>76.98705488190225</v>
       </c>
       <c r="L275">
         <v>943.8221945450973</v>
@@ -9346,15 +11073,27 @@
         <v>649.8932027231749</v>
       </c>
       <c r="N275">
+        <v>1593.715397268272</v>
+      </c>
+      <c r="O275">
+        <v>1.452272758955325</v>
+      </c>
+      <c r="P275">
+        <v>0.5922150191702155</v>
+      </c>
+      <c r="Q275">
+        <v>0.4077849808297846</v>
+      </c>
+      <c r="R275">
         <v>100.1555605809138</v>
       </c>
-      <c r="O275">
+      <c r="S275">
         <v>239.6167837678009</v>
       </c>
-      <c r="P275">
+      <c r="T275">
         <v>989.6655470718897</v>
       </c>
-      <c r="Q275">
+      <c r="U275">
         <v>1933.487741616987</v>
       </c>
     </row>
@@ -9392,7 +11131,7 @@
         <v>0.4</v>
       </c>
       <c r="K276">
-        <v>72.59999999999999</v>
+        <v>72.59545751769306</v>
       </c>
       <c r="L276">
         <v>836.9368144178011</v>
@@ -9401,15 +11140,27 @@
         <v>1739.210543282295</v>
       </c>
       <c r="N276">
+        <v>2576.147357700097</v>
+      </c>
+      <c r="O276">
+        <v>0.4812165023093215</v>
+      </c>
+      <c r="P276">
+        <v>0.3248792472667371</v>
+      </c>
+      <c r="Q276">
+        <v>0.6751207527332629</v>
+      </c>
+      <c r="R276">
         <v>108.0781756485363</v>
       </c>
-      <c r="O276">
+      <c r="S276">
         <v>323.9435781939345</v>
       </c>
-      <c r="P276">
+      <c r="T276">
         <v>2171.232297124766</v>
       </c>
-      <c r="Q276">
+      <c r="U276">
         <v>3008.169111542567</v>
       </c>
     </row>
@@ -9457,7 +11208,7 @@
         <v>0.5</v>
       </c>
       <c r="K278">
-        <v>76.7</v>
+        <v>76.72032259045787</v>
       </c>
       <c r="L278">
         <v>390.0624011098299</v>
@@ -9466,15 +11217,27 @@
         <v>1528.925042741863</v>
       </c>
       <c r="N278">
+        <v>1918.987443851693</v>
+      </c>
+      <c r="O278">
+        <v>0.255121991075717</v>
+      </c>
+      <c r="P278">
+        <v>0.2032646968897914</v>
+      </c>
+      <c r="Q278">
+        <v>0.7967353031102087</v>
+      </c>
+      <c r="R278">
         <v>131.5309800217799</v>
       </c>
-      <c r="O278">
+      <c r="S278">
         <v>234.49929184562</v>
       </c>
-      <c r="P278">
+      <c r="T278">
         <v>1894.955314609263</v>
       </c>
-      <c r="Q278">
+      <c r="U278">
         <v>2285.017715719093</v>
       </c>
     </row>
@@ -9512,7 +11275,7 @@
         <v>0.4</v>
       </c>
       <c r="K279">
-        <v>79.3</v>
+        <v>79.28299396491987</v>
       </c>
       <c r="L279">
         <v>162.8283101692388</v>
@@ -9521,15 +11284,27 @@
         <v>256.8560266264824</v>
       </c>
       <c r="N279">
+        <v>419.6843367957212</v>
+      </c>
+      <c r="O279">
+        <v>0.6339283228344189</v>
+      </c>
+      <c r="P279">
+        <v>0.3879780489603892</v>
+      </c>
+      <c r="Q279">
+        <v>0.6120219510396108</v>
+      </c>
+      <c r="R279">
         <v>31.67648684856648</v>
       </c>
-      <c r="O279">
+      <c r="S279">
         <v>38.68551638923534</v>
       </c>
-      <c r="P279">
+      <c r="T279">
         <v>327.2180298642842</v>
       </c>
-      <c r="Q279">
+      <c r="U279">
         <v>490.046340033523</v>
       </c>
     </row>
@@ -9567,7 +11342,7 @@
         <v>0.6</v>
       </c>
       <c r="K280">
-        <v>84.59999999999999</v>
+        <v>84.55690793666395</v>
       </c>
     </row>
     <row r="281">
@@ -9644,7 +11419,7 @@
         <v>0.4</v>
       </c>
       <c r="K285">
-        <v>74.7</v>
+        <v>74.67340140051388</v>
       </c>
       <c r="L285">
         <v>1929.126571215911</v>
@@ -9653,15 +11428,27 @@
         <v>1248.331182052063</v>
       </c>
       <c r="N285">
+        <v>3177.457753267974</v>
+      </c>
+      <c r="O285">
+        <v>1.545364402453463</v>
+      </c>
+      <c r="P285">
+        <v>0.6071289442737137</v>
+      </c>
+      <c r="Q285">
+        <v>0.3928710557262863</v>
+      </c>
+      <c r="R285">
         <v>135.2134789791506</v>
       </c>
-      <c r="O285">
+      <c r="S285">
         <v>358.3721376143585</v>
       </c>
-      <c r="P285">
+      <c r="T285">
         <v>1741.916798645572</v>
       </c>
-      <c r="Q285">
+      <c r="U285">
         <v>3671.043369861483</v>
       </c>
     </row>
@@ -9705,15 +11492,27 @@
         <v>497.0441382351096</v>
       </c>
       <c r="N286">
+        <v>1034.031016464489</v>
+      </c>
+      <c r="O286">
+        <v>1.080360549338933</v>
+      </c>
+      <c r="P286">
+        <v>0.5193140918203983</v>
+      </c>
+      <c r="Q286">
+        <v>0.4806859081796017</v>
+      </c>
+      <c r="R286">
         <v>103.4787627843177</v>
       </c>
-      <c r="O286">
+      <c r="S286">
         <v>119.6175289388053</v>
       </c>
-      <c r="P286">
+      <c r="T286">
         <v>720.1404299582326</v>
       </c>
-      <c r="Q286">
+      <c r="U286">
         <v>1257.127308187612</v>
       </c>
     </row>
@@ -9761,7 +11560,7 @@
         <v>0.3</v>
       </c>
       <c r="K288">
-        <v>87.8</v>
+        <v>87.81115878094565</v>
       </c>
     </row>
     <row r="289">
@@ -9818,7 +11617,7 @@
         <v>0.4</v>
       </c>
       <c r="K291">
-        <v>76.09999999999999</v>
+        <v>76.14962101793861</v>
       </c>
       <c r="L291">
         <v>622.2451998668454</v>
@@ -9827,15 +11626,27 @@
         <v>822.3368698886861</v>
       </c>
       <c r="N291">
+        <v>1444.582069755531</v>
+      </c>
+      <c r="O291">
+        <v>0.7566791939549959</v>
+      </c>
+      <c r="P291">
+        <v>0.430744097475991</v>
+      </c>
+      <c r="Q291">
+        <v>0.5692559025240091</v>
+      </c>
+      <c r="R291">
         <v>79.58123965220871</v>
       </c>
-      <c r="O291">
+      <c r="S291">
         <v>115.475061782774</v>
       </c>
-      <c r="P291">
+      <c r="T291">
         <v>1017.393171323669</v>
       </c>
-      <c r="Q291">
+      <c r="U291">
         <v>1639.638371190514</v>
       </c>
     </row>
@@ -9903,7 +11714,7 @@
         <v>0.4</v>
       </c>
       <c r="K295">
-        <v>82.7</v>
+        <v>82.74094803125053</v>
       </c>
       <c r="L295">
         <v>272.1433199802382</v>
@@ -9912,15 +11723,27 @@
         <v>302.3857812663552</v>
       </c>
       <c r="N295">
+        <v>574.5291012465934</v>
+      </c>
+      <c r="O295">
+        <v>0.8999871582603347</v>
+      </c>
+      <c r="P295">
+        <v>0.4736806532336673</v>
+      </c>
+      <c r="Q295">
+        <v>0.5263193467663325</v>
+      </c>
+      <c r="R295">
         <v>74.55402312728681</v>
       </c>
-      <c r="O295">
+      <c r="S295">
         <v>77.96011337208995</v>
       </c>
-      <c r="P295">
+      <c r="T295">
         <v>454.899917765732</v>
       </c>
-      <c r="Q295">
+      <c r="U295">
         <v>727.0432377459701</v>
       </c>
     </row>
@@ -9974,15 +11797,27 @@
         <v>359.6072136635596</v>
       </c>
       <c r="N297">
+        <v>905.1365376572315</v>
+      </c>
+      <c r="O297">
+        <v>1.517014407013695</v>
+      </c>
+      <c r="P297">
+        <v>0.602703902999726</v>
+      </c>
+      <c r="Q297">
+        <v>0.397296097000274</v>
+      </c>
+      <c r="R297">
         <v>62.03938816378327</v>
       </c>
-      <c r="O297">
+      <c r="S297">
         <v>81.56071910183174</v>
       </c>
-      <c r="P297">
+      <c r="T297">
         <v>503.2073209291746</v>
       </c>
-      <c r="Q297">
+      <c r="U297">
         <v>1048.736644922847</v>
       </c>
     </row>
@@ -10030,7 +11865,7 @@
         <v>0.4</v>
       </c>
       <c r="K299">
-        <v>72.7</v>
+        <v>72.68987142667117</v>
       </c>
       <c r="L299">
         <v>442.4345247599317</v>
@@ -10039,15 +11874,27 @@
         <v>970.2774286147055</v>
       </c>
       <c r="N299">
+        <v>1412.711953374637</v>
+      </c>
+      <c r="O299">
+        <v>0.455987650245156</v>
+      </c>
+      <c r="P299">
+        <v>0.3131809876054771</v>
+      </c>
+      <c r="Q299">
+        <v>0.6868190123945228</v>
+      </c>
+      <c r="R299">
         <v>105.4171922007052</v>
       </c>
-      <c r="O299">
+      <c r="S299">
         <v>172.7741246941918</v>
       </c>
-      <c r="P299">
+      <c r="T299">
         <v>1248.468745509603</v>
       </c>
-      <c r="Q299">
+      <c r="U299">
         <v>1690.903270269534</v>
       </c>
     </row>
@@ -10159,7 +12006,7 @@
         <v>0.5</v>
       </c>
       <c r="K305">
-        <v>78.90000000000001</v>
+        <v>78.87415194852542</v>
       </c>
       <c r="L305">
         <v>219.1295418135352</v>
@@ -10168,15 +12015,27 @@
         <v>128.639326160116</v>
       </c>
       <c r="N305">
+        <v>347.7688679736511</v>
+      </c>
+      <c r="O305">
+        <v>1.703441306438336</v>
+      </c>
+      <c r="P305">
+        <v>0.6301010872259493</v>
+      </c>
+      <c r="Q305">
+        <v>0.3698989127740507</v>
+      </c>
+      <c r="R305">
         <v>34.6830448772334</v>
       </c>
-      <c r="O305">
+      <c r="S305">
         <v>42.89028246126275</v>
       </c>
-      <c r="P305">
+      <c r="T305">
         <v>206.2126534986121</v>
       </c>
-      <c r="Q305">
+      <c r="U305">
         <v>425.3421953121473</v>
       </c>
     </row>
@@ -10224,7 +12083,7 @@
         <v>0.4</v>
       </c>
       <c r="K307">
-        <v>81.2</v>
+        <v>81.24196321637784</v>
       </c>
     </row>
   </sheetData>
